--- a/results/part2_region_fa/AI各区域不对称评分+GlobalFA原始值.xlsx
+++ b/results/part2_region_fa/AI各区域不对称评分+GlobalFA原始值.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:F101"/>
+  <dimension ref="A1:F284"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -451,2201 +451,6227 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>FA0001</t>
+          <t>1.对称轴133张/丁兰.JPG</t>
         </is>
       </c>
       <c r="B2" t="n">
-        <v>0.049048</v>
+        <v>0.039788</v>
       </c>
       <c r="C2" t="n">
-        <v>0.015237</v>
+        <v>0.022845</v>
       </c>
       <c r="D2" t="n">
-        <v>0.036917</v>
+        <v>0.022373</v>
       </c>
       <c r="E2" t="n">
-        <v>0.051513</v>
+        <v>0.047893</v>
       </c>
       <c r="F2" t="n">
-        <v>0.088173</v>
+        <v>0.046474</v>
       </c>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>FA0002</t>
+          <t>1.对称轴133张/丁柯文.JPG</t>
         </is>
       </c>
       <c r="B3" t="n">
-        <v>0.039952</v>
+        <v>0.015935</v>
       </c>
       <c r="C3" t="n">
-        <v>0.033764</v>
+        <v>0.012356</v>
       </c>
       <c r="D3" t="n">
-        <v>0.021229</v>
+        <v>0.009153</v>
       </c>
       <c r="E3" t="n">
-        <v>0.03466</v>
+        <v>0.027285</v>
       </c>
       <c r="F3" t="n">
-        <v>0.097997</v>
+        <v>0.06753199999999999</v>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>FA0003</t>
+          <t>1.对称轴133张/丁琳玲.JPG</t>
         </is>
       </c>
       <c r="B4" t="n">
-        <v>0.024193</v>
+        <v>0.027293</v>
       </c>
       <c r="C4" t="n">
-        <v>0.030447</v>
+        <v>0.013978</v>
       </c>
       <c r="D4" t="n">
-        <v>0.053745</v>
+        <v>0.01944</v>
       </c>
       <c r="E4" t="n">
-        <v>0.038728</v>
+        <v>0.014517</v>
       </c>
       <c r="F4" t="n">
-        <v>0.084568</v>
+        <v>0.006758</v>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>FA0004</t>
+          <t>1.对称轴133张/丰羽辰.JPG</t>
         </is>
       </c>
       <c r="B5" t="n">
-        <v>0.036578</v>
+        <v>0.02573</v>
       </c>
       <c r="C5" t="n">
-        <v>0.026401</v>
+        <v>0.012012</v>
       </c>
       <c r="D5" t="n">
-        <v>0.031431</v>
+        <v>0.008683</v>
       </c>
       <c r="E5" t="n">
-        <v>0.025633</v>
+        <v>0.006223</v>
       </c>
       <c r="F5" t="n">
-        <v>0.066843</v>
+        <v>0.046477</v>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>FA0005</t>
+          <t>1.对称轴133张/代凌旖.JPG</t>
         </is>
       </c>
       <c r="B6" t="n">
-        <v>0.047846</v>
+        <v>0.030885</v>
       </c>
       <c r="C6" t="n">
-        <v>0.039218</v>
+        <v>0.021252</v>
       </c>
       <c r="D6" t="n">
-        <v>0.029556</v>
+        <v>0.018493</v>
       </c>
       <c r="E6" t="n">
-        <v>0.067137</v>
+        <v>0.041611</v>
       </c>
       <c r="F6" t="n">
-        <v>0.097911</v>
+        <v>0.018345</v>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>FA0006</t>
+          <t>1.对称轴133张/代四琼.JPG</t>
         </is>
       </c>
       <c r="B7" t="n">
-        <v>0.025199</v>
+        <v>0.028883</v>
       </c>
       <c r="C7" t="n">
-        <v>0.009154000000000001</v>
+        <v>0.018856</v>
       </c>
       <c r="D7" t="n">
-        <v>0.011528</v>
+        <v>0.01228</v>
       </c>
       <c r="E7" t="n">
-        <v>0.021926</v>
+        <v>0.022604</v>
       </c>
       <c r="F7" t="n">
-        <v>0.032394</v>
+        <v>0.043603</v>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>FA0007</t>
+          <t>1.对称轴133张/代玉婷.JPG</t>
         </is>
       </c>
       <c r="B8" t="n">
-        <v>0.055265</v>
+        <v>0.029952</v>
       </c>
       <c r="C8" t="n">
-        <v>0.024412</v>
+        <v>0.02119</v>
       </c>
       <c r="D8" t="n">
-        <v>0.018636</v>
+        <v>0.019275</v>
       </c>
       <c r="E8" t="n">
-        <v>0.022578</v>
+        <v>0.022396</v>
       </c>
       <c r="F8" t="n">
-        <v>0.129474</v>
+        <v>0.038073</v>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>FA0008</t>
+          <t>1.对称轴133张/代芯妮.JPG</t>
         </is>
       </c>
       <c r="B9" t="n">
-        <v>0.036513</v>
+        <v>0.037308</v>
       </c>
       <c r="C9" t="n">
-        <v>0.011102</v>
+        <v>0.020203</v>
       </c>
       <c r="D9" t="n">
-        <v>0.014296</v>
+        <v>0.008300999999999999</v>
       </c>
       <c r="E9" t="n">
-        <v>0.033488</v>
+        <v>0.029422</v>
       </c>
       <c r="F9" t="n">
-        <v>0.06596399999999999</v>
+        <v>0.049261</v>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>FA0009</t>
+          <t>1.对称轴133张/党琪越.JPG</t>
         </is>
       </c>
       <c r="B10" t="n">
-        <v>0.034066</v>
+        <v>0.024171</v>
       </c>
       <c r="C10" t="n">
-        <v>0.018279</v>
+        <v>0.009748</v>
       </c>
       <c r="D10" t="n">
-        <v>0.024441</v>
+        <v>0.033478</v>
       </c>
       <c r="E10" t="n">
-        <v>0.041308</v>
+        <v>0.022846</v>
       </c>
       <c r="F10" t="n">
-        <v>0.045451</v>
+        <v>0.06203</v>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>FA0010</t>
+          <t>1.对称轴133张/刁聪.JPG</t>
         </is>
       </c>
       <c r="B11" t="n">
-        <v>0.061667</v>
+        <v>0.020991</v>
       </c>
       <c r="C11" t="n">
-        <v>0.025212</v>
+        <v>0.01377</v>
       </c>
       <c r="D11" t="n">
-        <v>0.02951</v>
+        <v>0.02254</v>
       </c>
       <c r="E11" t="n">
-        <v>0.025981</v>
+        <v>0.031813</v>
       </c>
       <c r="F11" t="n">
-        <v>0.186972</v>
+        <v>0.051232</v>
       </c>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>FA0011</t>
+          <t>1.对称轴133张/崔力坤.JPG</t>
         </is>
       </c>
       <c r="B12" t="n">
-        <v>0.030344</v>
+        <v>0.016281</v>
       </c>
       <c r="C12" t="n">
-        <v>0.01314</v>
+        <v>0.009893000000000001</v>
       </c>
       <c r="D12" t="n">
-        <v>0.018329</v>
+        <v>0.008203</v>
       </c>
       <c r="E12" t="n">
-        <v>0.039191</v>
+        <v>0.019063</v>
       </c>
       <c r="F12" t="n">
-        <v>0.149996</v>
+        <v>0.012196</v>
       </c>
     </row>
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>FA0012</t>
+          <t>1.对称轴133张/巴比诺.JPG</t>
         </is>
       </c>
       <c r="B13" t="n">
-        <v>0.052573</v>
+        <v>0.054936</v>
       </c>
       <c r="C13" t="n">
-        <v>0.022145</v>
+        <v>0.027488</v>
       </c>
       <c r="D13" t="n">
-        <v>0.015883</v>
+        <v>0.018797</v>
       </c>
       <c r="E13" t="n">
-        <v>0.030794</v>
+        <v>0.021639</v>
       </c>
       <c r="F13" t="n">
-        <v>0.046467</v>
+        <v>0.088889</v>
       </c>
     </row>
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>FA0013</t>
+          <t>1.对称轴133张/德吉龙珍.JPG</t>
         </is>
       </c>
       <c r="B14" t="n">
-        <v>0.036074</v>
+        <v>0.027017</v>
       </c>
       <c r="C14" t="n">
-        <v>0.016323</v>
+        <v>0.023419</v>
       </c>
       <c r="D14" t="n">
-        <v>0.011765</v>
+        <v>0.025594</v>
       </c>
       <c r="E14" t="n">
-        <v>0.027667</v>
+        <v>0.035603</v>
       </c>
       <c r="F14" t="n">
-        <v>0.117295</v>
+        <v>0.096761</v>
       </c>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>FA0014</t>
+          <t>1.对称轴133张/戴昀纭.JPG</t>
         </is>
       </c>
       <c r="B15" t="n">
-        <v>0.029677</v>
+        <v>0.02874</v>
       </c>
       <c r="C15" t="n">
-        <v>0.01037</v>
+        <v>0.006957</v>
       </c>
       <c r="D15" t="n">
-        <v>0.025182</v>
+        <v>0.028338</v>
       </c>
       <c r="E15" t="n">
-        <v>0.02063</v>
+        <v>0.030346</v>
       </c>
       <c r="F15" t="n">
-        <v>0.075831</v>
+        <v>0.017838</v>
       </c>
     </row>
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>FA0015</t>
+          <t>1.对称轴133张/戴瑜宸.JPG</t>
         </is>
       </c>
       <c r="B16" t="n">
-        <v>0.037449</v>
+        <v>0.020937</v>
       </c>
       <c r="C16" t="n">
-        <v>0.022069</v>
+        <v>0.010739</v>
       </c>
       <c r="D16" t="n">
-        <v>0.00423</v>
+        <v>0.004337</v>
       </c>
       <c r="E16" t="n">
-        <v>0.018273</v>
+        <v>0.010044</v>
       </c>
       <c r="F16" t="n">
-        <v>0.050686</v>
+        <v>0.022059</v>
       </c>
     </row>
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>FA0016</t>
+          <t>1.对称轴133张/方利.JPG</t>
         </is>
       </c>
       <c r="B17" t="n">
-        <v>0.050415</v>
+        <v>0.025644</v>
       </c>
       <c r="C17" t="n">
-        <v>0.035488</v>
+        <v>0.021088</v>
       </c>
       <c r="D17" t="n">
-        <v>0.046747</v>
+        <v>0.021615</v>
       </c>
       <c r="E17" t="n">
-        <v>0.061756</v>
+        <v>0.04301</v>
       </c>
       <c r="F17" t="n">
-        <v>0.099566</v>
+        <v>0.085314</v>
       </c>
     </row>
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>FA0017</t>
+          <t>1.对称轴133张/方媛.JPG</t>
         </is>
       </c>
       <c r="B18" t="n">
-        <v>0.06553299999999999</v>
+        <v>0.029285</v>
       </c>
       <c r="C18" t="n">
-        <v>0.010018</v>
+        <v>0.008881</v>
       </c>
       <c r="D18" t="n">
-        <v>0.01687</v>
+        <v>0.00153</v>
       </c>
       <c r="E18" t="n">
-        <v>0.042672</v>
+        <v>0.01737</v>
       </c>
       <c r="F18" t="n">
-        <v>0.061808</v>
+        <v>0.004464</v>
       </c>
     </row>
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>FA0018</t>
+          <t>1.对称轴133张/方明杰.JPG</t>
         </is>
       </c>
       <c r="B19" t="n">
-        <v>0.031683</v>
+        <v>0.012113</v>
       </c>
       <c r="C19" t="n">
-        <v>0.021616</v>
+        <v>0.018012</v>
       </c>
       <c r="D19" t="n">
-        <v>0.063317</v>
+        <v>0.033148</v>
       </c>
       <c r="E19" t="n">
-        <v>0.030827</v>
+        <v>0.020837</v>
       </c>
       <c r="F19" t="n">
-        <v>0.046678</v>
+        <v>0.06461</v>
       </c>
     </row>
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
-          <t>FA0019</t>
+          <t>1.对称轴133张/方渝.JPG</t>
         </is>
       </c>
       <c r="B20" t="n">
-        <v>0.033097</v>
+        <v>0.011125</v>
       </c>
       <c r="C20" t="n">
-        <v>0.018433</v>
+        <v>0.01752</v>
       </c>
       <c r="D20" t="n">
-        <v>0.047742</v>
+        <v>0.023011</v>
       </c>
       <c r="E20" t="n">
-        <v>0.039823</v>
+        <v>0.013503</v>
       </c>
       <c r="F20" t="n">
-        <v>0.11766</v>
+        <v>0.037975</v>
       </c>
     </row>
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
-          <t>FA0020</t>
+          <t>1.对称轴133张/方策一.JPG</t>
         </is>
       </c>
       <c r="B21" t="n">
-        <v>0.053253</v>
+        <v>0.011863</v>
       </c>
       <c r="C21" t="n">
-        <v>0.015908</v>
+        <v>0.012628</v>
       </c>
       <c r="D21" t="n">
-        <v>0.018579</v>
+        <v>0.013035</v>
       </c>
       <c r="E21" t="n">
-        <v>0.022718</v>
+        <v>0.01199</v>
       </c>
       <c r="F21" t="n">
-        <v>0.070968</v>
+        <v>0.04293</v>
       </c>
     </row>
     <row r="22">
       <c r="A22" t="inlineStr">
         <is>
-          <t>FA0021</t>
+          <t>1.对称轴133张/曹强.JPG</t>
         </is>
       </c>
       <c r="B22" t="n">
-        <v>0.025784</v>
+        <v>0.030376</v>
       </c>
       <c r="C22" t="n">
-        <v>0.012591</v>
+        <v>0.023532</v>
       </c>
       <c r="D22" t="n">
-        <v>0.007374</v>
+        <v>0.006475</v>
       </c>
       <c r="E22" t="n">
-        <v>0.040379</v>
+        <v>0.028343</v>
       </c>
       <c r="F22" t="n">
-        <v>0.083352</v>
+        <v>0.081152</v>
       </c>
     </row>
     <row r="23">
       <c r="A23" t="inlineStr">
         <is>
-          <t>FA0022</t>
+          <t>1.对称轴133张/曹志颐.JPG</t>
         </is>
       </c>
       <c r="B23" t="n">
-        <v>0.046818</v>
+        <v>0.015256</v>
       </c>
       <c r="C23" t="n">
-        <v>0.019562</v>
+        <v>0.020022</v>
       </c>
       <c r="D23" t="n">
-        <v>0.025509</v>
+        <v>0.032923</v>
       </c>
       <c r="E23" t="n">
-        <v>0.039803</v>
+        <v>0.023225</v>
       </c>
       <c r="F23" t="n">
-        <v>0.083331</v>
+        <v>0.040593</v>
       </c>
     </row>
     <row r="24">
       <c r="A24" t="inlineStr">
         <is>
-          <t>FA0023</t>
+          <t>1.对称轴133张/曹歆呓.JPG</t>
         </is>
       </c>
       <c r="B24" t="n">
-        <v>0.043185</v>
+        <v>0.027797</v>
       </c>
       <c r="C24" t="n">
-        <v>0.02054</v>
+        <v>0.019436</v>
       </c>
       <c r="D24" t="n">
-        <v>0.012259</v>
+        <v>0.006722</v>
       </c>
       <c r="E24" t="n">
-        <v>0.031753</v>
+        <v>0.015579</v>
       </c>
       <c r="F24" t="n">
-        <v>0.08372499999999999</v>
+        <v>0.056675</v>
       </c>
     </row>
     <row r="25">
       <c r="A25" t="inlineStr">
         <is>
-          <t>FA0024</t>
+          <t>1.对称轴133张/曹玉兰.JPG</t>
         </is>
       </c>
       <c r="B25" t="n">
-        <v>0.035144</v>
+        <v>0.038732</v>
       </c>
       <c r="C25" t="n">
-        <v>0.012785</v>
+        <v>0.021756</v>
       </c>
       <c r="D25" t="n">
-        <v>0.038751</v>
+        <v>0.026691</v>
       </c>
       <c r="E25" t="n">
-        <v>0.022645</v>
+        <v>0.021251</v>
       </c>
       <c r="F25" t="n">
-        <v>0.020947</v>
+        <v>0.034696</v>
       </c>
     </row>
     <row r="26">
       <c r="A26" t="inlineStr">
         <is>
-          <t>FA0025</t>
+          <t>1.对称轴133张/曾世杰.JPG</t>
         </is>
       </c>
       <c r="B26" t="n">
-        <v>0.042303</v>
+        <v>0.063294</v>
       </c>
       <c r="C26" t="n">
-        <v>0.030217</v>
+        <v>0.033725</v>
       </c>
       <c r="D26" t="n">
-        <v>0.035143</v>
+        <v>0.051572</v>
       </c>
       <c r="E26" t="n">
-        <v>0.04082</v>
+        <v>0.055897</v>
       </c>
       <c r="F26" t="n">
-        <v>0.11358</v>
+        <v>0.036006</v>
       </c>
     </row>
     <row r="27">
       <c r="A27" t="inlineStr">
         <is>
-          <t>FA0026</t>
+          <t>1.对称轴133张/曾众婉.JPG</t>
         </is>
       </c>
       <c r="B27" t="n">
-        <v>0.035116</v>
+        <v>0.02643</v>
       </c>
       <c r="C27" t="n">
-        <v>0.025225</v>
+        <v>0.025938</v>
       </c>
       <c r="D27" t="n">
-        <v>0.014392</v>
+        <v>0.012558</v>
       </c>
       <c r="E27" t="n">
-        <v>0.024125</v>
+        <v>0.041214</v>
       </c>
       <c r="F27" t="n">
-        <v>0.086934</v>
+        <v>0.07072199999999999</v>
       </c>
     </row>
     <row r="28">
       <c r="A28" t="inlineStr">
         <is>
-          <t>FA0027</t>
+          <t>1.对称轴133张/曾佳.JPG</t>
         </is>
       </c>
       <c r="B28" t="n">
-        <v>0.038892</v>
+        <v>0.04636</v>
       </c>
       <c r="C28" t="n">
-        <v>0.011919</v>
+        <v>0.01647</v>
       </c>
       <c r="D28" t="n">
-        <v>0.024842</v>
+        <v>0.022862</v>
       </c>
       <c r="E28" t="n">
-        <v>0.014531</v>
+        <v>0.029366</v>
       </c>
       <c r="F28" t="n">
-        <v>0.063204</v>
+        <v>0.025685</v>
       </c>
     </row>
     <row r="29">
       <c r="A29" t="inlineStr">
         <is>
-          <t>FA0028</t>
+          <t>1.对称轴133张/曾元静.JPG</t>
         </is>
       </c>
       <c r="B29" t="n">
-        <v>0.054334</v>
+        <v>0.036857</v>
       </c>
       <c r="C29" t="n">
-        <v>0.027494</v>
+        <v>0.020392</v>
       </c>
       <c r="D29" t="n">
-        <v>0.025218</v>
+        <v>0.014741</v>
       </c>
       <c r="E29" t="n">
-        <v>0.040349</v>
+        <v>0.037932</v>
       </c>
       <c r="F29" t="n">
-        <v>0.102207</v>
+        <v>0.012219</v>
       </c>
     </row>
     <row r="30">
       <c r="A30" t="inlineStr">
         <is>
-          <t>FA0029</t>
+          <t>1.对称轴133张/曾夏.JPG</t>
         </is>
       </c>
       <c r="B30" t="n">
-        <v>0.064162</v>
+        <v>0.049451</v>
       </c>
       <c r="C30" t="n">
-        <v>0.03117</v>
+        <v>0.013387</v>
       </c>
       <c r="D30" t="n">
-        <v>0.022736</v>
+        <v>0.051922</v>
       </c>
       <c r="E30" t="n">
-        <v>0.064521</v>
+        <v>0.031565</v>
       </c>
       <c r="F30" t="n">
-        <v>0.118002</v>
+        <v>0.09393799999999999</v>
       </c>
     </row>
     <row r="31">
       <c r="A31" t="inlineStr">
         <is>
-          <t>FA0030</t>
+          <t>1.对称轴133张/曾子涵.JPG</t>
         </is>
       </c>
       <c r="B31" t="n">
-        <v>0.019223</v>
+        <v>0.034093</v>
       </c>
       <c r="C31" t="n">
-        <v>0.016906</v>
+        <v>0.021866</v>
       </c>
       <c r="D31" t="n">
-        <v>0.010576</v>
+        <v>0.02147</v>
       </c>
       <c r="E31" t="n">
-        <v>0.014009</v>
+        <v>0.040598</v>
       </c>
       <c r="F31" t="n">
-        <v>0.035191</v>
+        <v>0.018148</v>
       </c>
     </row>
     <row r="32">
       <c r="A32" t="inlineStr">
         <is>
-          <t>FA0031</t>
+          <t>1.对称轴133张/曾少阳.JPG</t>
         </is>
       </c>
       <c r="B32" t="n">
-        <v>0.048213</v>
+        <v>0.009226</v>
       </c>
       <c r="C32" t="n">
-        <v>0.017948</v>
+        <v>0.023521</v>
       </c>
       <c r="D32" t="n">
-        <v>0.042673</v>
+        <v>0.014322</v>
       </c>
       <c r="E32" t="n">
-        <v>0.03659</v>
+        <v>0.012474</v>
       </c>
       <c r="F32" t="n">
-        <v>0.097743</v>
+        <v>0.020874</v>
       </c>
     </row>
     <row r="33">
       <c r="A33" t="inlineStr">
         <is>
-          <t>FA0032</t>
+          <t>1.对称轴133张/曾星.JPG</t>
         </is>
       </c>
       <c r="B33" t="n">
-        <v>0.055532</v>
+        <v>0.016575</v>
       </c>
       <c r="C33" t="n">
-        <v>0.024912</v>
+        <v>0.021061</v>
       </c>
       <c r="D33" t="n">
-        <v>0.027455</v>
+        <v>0.007048</v>
       </c>
       <c r="E33" t="n">
-        <v>0.031855</v>
+        <v>0.0116</v>
       </c>
       <c r="F33" t="n">
-        <v>0.071808</v>
+        <v>0.028046</v>
       </c>
     </row>
     <row r="34">
       <c r="A34" t="inlineStr">
         <is>
-          <t>FA0033</t>
+          <t>1.对称轴133张/曾朝龙.JPG</t>
         </is>
       </c>
       <c r="B34" t="n">
-        <v>0.024462</v>
+        <v>0.028825</v>
       </c>
       <c r="C34" t="n">
-        <v>0.019726</v>
+        <v>0.012256</v>
       </c>
       <c r="D34" t="n">
-        <v>0.006159</v>
+        <v>0.012185</v>
       </c>
       <c r="E34" t="n">
-        <v>0.025464</v>
+        <v>0.034858</v>
       </c>
       <c r="F34" t="n">
-        <v>0.034464</v>
+        <v>0.039909</v>
       </c>
     </row>
     <row r="35">
       <c r="A35" t="inlineStr">
         <is>
-          <t>FA0034</t>
+          <t>1.对称轴133张/曾楚涵.JPG</t>
         </is>
       </c>
       <c r="B35" t="n">
-        <v>0.035709</v>
+        <v>0.037367</v>
       </c>
       <c r="C35" t="n">
-        <v>0.016636</v>
+        <v>0.020909</v>
       </c>
       <c r="D35" t="n">
-        <v>0.013488</v>
+        <v>0.01101</v>
       </c>
       <c r="E35" t="n">
-        <v>0.042995</v>
+        <v>0.013569</v>
       </c>
       <c r="F35" t="n">
-        <v>0.131177</v>
+        <v>0.056112</v>
       </c>
     </row>
     <row r="36">
       <c r="A36" t="inlineStr">
         <is>
-          <t>FA0035</t>
+          <t>1.对称轴133张/曾献文.JPG</t>
         </is>
       </c>
       <c r="B36" t="n">
-        <v>0.093275</v>
+        <v>0.029872</v>
       </c>
       <c r="C36" t="n">
-        <v>0.026534</v>
+        <v>0.010028</v>
       </c>
       <c r="D36" t="n">
-        <v>0.024029</v>
+        <v>0.011447</v>
       </c>
       <c r="E36" t="n">
-        <v>0.023185</v>
+        <v>0.021076</v>
       </c>
       <c r="F36" t="n">
-        <v>0.034888</v>
+        <v>0.042403</v>
       </c>
     </row>
     <row r="37">
       <c r="A37" t="inlineStr">
         <is>
-          <t>FA0036</t>
+          <t>1.对称轴133张/曾璐.JPG</t>
         </is>
       </c>
       <c r="B37" t="n">
-        <v>0.053736</v>
+        <v>0.026164</v>
       </c>
       <c r="C37" t="n">
-        <v>0.031775</v>
+        <v>0.017141</v>
       </c>
       <c r="D37" t="n">
-        <v>0.032712</v>
+        <v>0.036262</v>
       </c>
       <c r="E37" t="n">
-        <v>0.039355</v>
+        <v>0.010675</v>
       </c>
       <c r="F37" t="n">
-        <v>0.049522</v>
+        <v>0.06109</v>
       </c>
     </row>
     <row r="38">
       <c r="A38" t="inlineStr">
         <is>
-          <t>FA0037</t>
+          <t>1.对称轴133张/曾铭浩.JPG</t>
         </is>
       </c>
       <c r="B38" t="n">
-        <v>0.039724</v>
+        <v>0.03798</v>
       </c>
       <c r="C38" t="n">
-        <v>0.010269</v>
+        <v>0.009135000000000001</v>
       </c>
       <c r="D38" t="n">
-        <v>0.070922</v>
+        <v>0.008196999999999999</v>
       </c>
       <c r="E38" t="n">
-        <v>0.022403</v>
+        <v>0.01264</v>
       </c>
       <c r="F38" t="n">
-        <v>0.045919</v>
+        <v>0.066342</v>
       </c>
     </row>
     <row r="39">
       <c r="A39" t="inlineStr">
         <is>
-          <t>FA0038</t>
+          <t>1.对称轴133张/曾青云.JPG</t>
         </is>
       </c>
       <c r="B39" t="n">
-        <v>0.037561</v>
+        <v>0.044839</v>
       </c>
       <c r="C39" t="n">
-        <v>0.03414</v>
+        <v>0.015975</v>
       </c>
       <c r="D39" t="n">
-        <v>0.023391</v>
+        <v>0.010715</v>
       </c>
       <c r="E39" t="n">
-        <v>0.030959</v>
+        <v>0.009488</v>
       </c>
       <c r="F39" t="n">
-        <v>0.03031</v>
+        <v>0.036805</v>
       </c>
     </row>
     <row r="40">
       <c r="A40" t="inlineStr">
         <is>
-          <t>FA0039</t>
+          <t>1.对称轴133张/曾馨琪.JPG</t>
         </is>
       </c>
       <c r="B40" t="n">
-        <v>0.019118</v>
+        <v>0.017693</v>
       </c>
       <c r="C40" t="n">
-        <v>0.013062</v>
+        <v>0.020934</v>
       </c>
       <c r="D40" t="n">
-        <v>0.027889</v>
+        <v>0.015728</v>
       </c>
       <c r="E40" t="n">
-        <v>0.019461</v>
+        <v>0.023382</v>
       </c>
       <c r="F40" t="n">
-        <v>0.048135</v>
+        <v>0.02228</v>
       </c>
     </row>
     <row r="41">
       <c r="A41" t="inlineStr">
         <is>
-          <t>FA0040</t>
+          <t>1.对称轴133张/杜娟.JPG</t>
         </is>
       </c>
       <c r="B41" t="n">
-        <v>0.043118</v>
+        <v>0.013909</v>
       </c>
       <c r="C41" t="n">
-        <v>0.014669</v>
+        <v>0.017714</v>
       </c>
       <c r="D41" t="n">
-        <v>0.011645</v>
+        <v>0.009838</v>
       </c>
       <c r="E41" t="n">
-        <v>0.042508</v>
+        <v>0.014068</v>
       </c>
       <c r="F41" t="n">
-        <v>0.059493</v>
+        <v>0.070795</v>
       </c>
     </row>
     <row r="42">
       <c r="A42" t="inlineStr">
         <is>
-          <t>FA0041</t>
+          <t>1.对称轴133张/杜晟泽.JPG</t>
         </is>
       </c>
       <c r="B42" t="n">
-        <v>0.033523</v>
+        <v>0.029185</v>
       </c>
       <c r="C42" t="n">
-        <v>0.009461000000000001</v>
+        <v>0.011391</v>
       </c>
       <c r="D42" t="n">
-        <v>0.021155</v>
+        <v>0.033043</v>
       </c>
       <c r="E42" t="n">
-        <v>0.016808</v>
+        <v>0.044617</v>
       </c>
       <c r="F42" t="n">
-        <v>0.041694</v>
+        <v>0.102553</v>
       </c>
     </row>
     <row r="43">
       <c r="A43" t="inlineStr">
         <is>
-          <t>FA0042</t>
+          <t>1.对称轴133张/杜磊.JPG</t>
         </is>
       </c>
       <c r="B43" t="n">
-        <v>0.068132</v>
+        <v>0.039448</v>
       </c>
       <c r="C43" t="n">
-        <v>0.04223</v>
+        <v>0.019159</v>
       </c>
       <c r="D43" t="n">
-        <v>0.058508</v>
+        <v>0.031485</v>
       </c>
       <c r="E43" t="n">
-        <v>0.070266</v>
+        <v>0.020403</v>
       </c>
       <c r="F43" t="n">
-        <v>0.024492</v>
+        <v>0.075445</v>
       </c>
     </row>
     <row r="44">
       <c r="A44" t="inlineStr">
         <is>
-          <t>FA0043</t>
+          <t>1.对称轴133张/查星.JPG</t>
         </is>
       </c>
       <c r="B44" t="n">
-        <v>0.034725</v>
+        <v>0.018317</v>
       </c>
       <c r="C44" t="n">
-        <v>0.016969</v>
+        <v>0.017281</v>
       </c>
       <c r="D44" t="n">
-        <v>0.006625</v>
+        <v>0.015332</v>
       </c>
       <c r="E44" t="n">
-        <v>0.024973</v>
+        <v>0.016986</v>
       </c>
       <c r="F44" t="n">
-        <v>0.029918</v>
+        <v>0.021853</v>
       </c>
     </row>
     <row r="45">
       <c r="A45" t="inlineStr">
         <is>
-          <t>FA0044</t>
+          <t>1.对称轴133张/樊凤清.JPG</t>
         </is>
       </c>
       <c r="B45" t="n">
-        <v>0.032321</v>
+        <v>0.01401</v>
       </c>
       <c r="C45" t="n">
-        <v>0.026539</v>
+        <v>0.017848</v>
       </c>
       <c r="D45" t="n">
-        <v>0.044607</v>
+        <v>0.003752</v>
       </c>
       <c r="E45" t="n">
-        <v>0.043204</v>
+        <v>0.025866</v>
       </c>
       <c r="F45" t="n">
-        <v>0.09329999999999999</v>
+        <v>0.026181</v>
       </c>
     </row>
     <row r="46">
       <c r="A46" t="inlineStr">
         <is>
-          <t>FA0045</t>
+          <t>1.对称轴133张/樊芷萁.JPG</t>
         </is>
       </c>
       <c r="B46" t="n">
-        <v>0.034132</v>
+        <v>0.025832</v>
       </c>
       <c r="C46" t="n">
-        <v>0.013995</v>
+        <v>0.026238</v>
       </c>
       <c r="D46" t="n">
-        <v>0.002312</v>
+        <v>0.028757</v>
       </c>
       <c r="E46" t="n">
-        <v>0.011306</v>
+        <v>0.040792</v>
       </c>
       <c r="F46" t="n">
-        <v>0.024633</v>
+        <v>0.089198</v>
       </c>
     </row>
     <row r="47">
       <c r="A47" t="inlineStr">
         <is>
-          <t>FA0046</t>
+          <t>1.对称轴133张/段亦宵.JPG</t>
         </is>
       </c>
       <c r="B47" t="n">
-        <v>0.035112</v>
+        <v>0.026426</v>
       </c>
       <c r="C47" t="n">
-        <v>0.021793</v>
+        <v>0.010928</v>
       </c>
       <c r="D47" t="n">
-        <v>0.014823</v>
+        <v>0.012003</v>
       </c>
       <c r="E47" t="n">
-        <v>0.035617</v>
+        <v>0.033555</v>
       </c>
       <c r="F47" t="n">
-        <v>0.034804</v>
+        <v>0.036362</v>
       </c>
     </row>
     <row r="48">
       <c r="A48" t="inlineStr">
         <is>
-          <t>FA0047</t>
+          <t>1.对称轴133张/段傲.JPG</t>
         </is>
       </c>
       <c r="B48" t="n">
-        <v>0.028866</v>
+        <v>0.020321</v>
       </c>
       <c r="C48" t="n">
-        <v>0.024164</v>
+        <v>0.023966</v>
       </c>
       <c r="D48" t="n">
-        <v>0.023093</v>
+        <v>0.017898</v>
       </c>
       <c r="E48" t="n">
-        <v>0.032304</v>
+        <v>0.027415</v>
       </c>
       <c r="F48" t="n">
-        <v>0.046142</v>
+        <v>0.060929</v>
       </c>
     </row>
     <row r="49">
       <c r="A49" t="inlineStr">
         <is>
-          <t>FA0048</t>
+          <t>1.对称轴133张/段嘉琪.JPG</t>
         </is>
       </c>
       <c r="B49" t="n">
-        <v>0.03918</v>
+        <v>0.018472</v>
       </c>
       <c r="C49" t="n">
-        <v>0.029387</v>
+        <v>0.011149</v>
       </c>
       <c r="D49" t="n">
-        <v>0.041799</v>
+        <v>0.006745</v>
       </c>
       <c r="E49" t="n">
-        <v>0.015704</v>
+        <v>0.021046</v>
       </c>
       <c r="F49" t="n">
-        <v>0.06443500000000001</v>
+        <v>0.09260699999999999</v>
       </c>
     </row>
     <row r="50">
       <c r="A50" t="inlineStr">
         <is>
-          <t>FA0049</t>
+          <t>1.对称轴133张/白中天.JPG</t>
         </is>
       </c>
       <c r="B50" t="n">
-        <v>0.102599</v>
+        <v>0.031528</v>
       </c>
       <c r="C50" t="n">
-        <v>0.02384</v>
+        <v>0.021636</v>
       </c>
       <c r="D50" t="n">
-        <v>0.057524</v>
+        <v>0.017037</v>
       </c>
       <c r="E50" t="n">
-        <v>0.052178</v>
+        <v>0.037235</v>
       </c>
       <c r="F50" t="n">
-        <v>0.177273</v>
+        <v>0.09597700000000001</v>
       </c>
     </row>
     <row r="51">
       <c r="A51" t="inlineStr">
         <is>
-          <t>FA0050</t>
+          <t>1.对称轴133张/白玛玉珍.JPG</t>
         </is>
       </c>
       <c r="B51" t="n">
-        <v>0.089861</v>
+        <v>0.027253</v>
       </c>
       <c r="C51" t="n">
-        <v>0.030644</v>
+        <v>0.036707</v>
       </c>
       <c r="D51" t="n">
-        <v>0.014453</v>
+        <v>0.031151</v>
       </c>
       <c r="E51" t="n">
-        <v>0.047227</v>
+        <v>0.060331</v>
       </c>
       <c r="F51" t="n">
-        <v>0.021077</v>
+        <v>0.082066</v>
       </c>
     </row>
     <row r="52">
       <c r="A52" t="inlineStr">
         <is>
-          <t>FA0051</t>
+          <t>1.对称轴133张/白雨.JPG</t>
         </is>
       </c>
       <c r="B52" t="n">
-        <v>0.054217</v>
+        <v>0.012886</v>
       </c>
       <c r="C52" t="n">
-        <v>0.027372</v>
+        <v>0.011223</v>
       </c>
       <c r="D52" t="n">
-        <v>0.015503</v>
+        <v>0.008749</v>
       </c>
       <c r="E52" t="n">
-        <v>0.033951</v>
+        <v>0.016557</v>
       </c>
       <c r="F52" t="n">
-        <v>0.050975</v>
+        <v>0.032394</v>
       </c>
     </row>
     <row r="53">
       <c r="A53" t="inlineStr">
         <is>
-          <t>FA0052</t>
+          <t>1.对称轴133张/程丹彤.JPG</t>
         </is>
       </c>
       <c r="B53" t="n">
-        <v>0.075042</v>
+        <v>0.04968</v>
       </c>
       <c r="C53" t="n">
-        <v>0.023436</v>
+        <v>0.046038</v>
       </c>
       <c r="D53" t="n">
-        <v>0.035544</v>
+        <v>0.027828</v>
       </c>
       <c r="E53" t="n">
-        <v>0.020756</v>
+        <v>0.079357</v>
       </c>
       <c r="F53" t="n">
-        <v>0.028349</v>
+        <v>0.074286</v>
       </c>
     </row>
     <row r="54">
       <c r="A54" t="inlineStr">
         <is>
-          <t>FA0053</t>
+          <t>1.对称轴133张/程兮.JPG</t>
         </is>
       </c>
       <c r="B54" t="n">
-        <v>0.064011</v>
+        <v>0.04512</v>
       </c>
       <c r="C54" t="n">
-        <v>0.021608</v>
+        <v>0.018117</v>
       </c>
       <c r="D54" t="n">
-        <v>0.021572</v>
+        <v>0.011742</v>
       </c>
       <c r="E54" t="n">
-        <v>0.047041</v>
+        <v>0.010129</v>
       </c>
       <c r="F54" t="n">
-        <v>0.118262</v>
+        <v>0.046194</v>
       </c>
     </row>
     <row r="55">
       <c r="A55" t="inlineStr">
         <is>
-          <t>FA0054</t>
+          <t>1.对称轴133张/程嘉辉.JPG</t>
         </is>
       </c>
       <c r="B55" t="n">
-        <v>0.04909</v>
+        <v>0.027325</v>
       </c>
       <c r="C55" t="n">
-        <v>0.017732</v>
+        <v>0.010577</v>
       </c>
       <c r="D55" t="n">
-        <v>0.008836999999999999</v>
+        <v>0.028014</v>
       </c>
       <c r="E55" t="n">
-        <v>0.020431</v>
+        <v>0.028856</v>
       </c>
       <c r="F55" t="n">
-        <v>0.028171</v>
+        <v>0.021407</v>
       </c>
     </row>
     <row r="56">
       <c r="A56" t="inlineStr">
         <is>
-          <t>FA0055</t>
+          <t>1.对称轴133张/程源.JPG</t>
         </is>
       </c>
       <c r="B56" t="n">
-        <v>0.032327</v>
+        <v>0.027371</v>
       </c>
       <c r="C56" t="n">
-        <v>0.015716</v>
+        <v>0.023942</v>
       </c>
       <c r="D56" t="n">
-        <v>0.006323</v>
+        <v>0.055632</v>
       </c>
       <c r="E56" t="n">
-        <v>0.018955</v>
+        <v>0.07185800000000001</v>
       </c>
       <c r="F56" t="n">
-        <v>0.0186</v>
+        <v>0.126193</v>
       </c>
     </row>
     <row r="57">
       <c r="A57" t="inlineStr">
         <is>
-          <t>FA0056</t>
+          <t>1.对称轴133张/程琪语.JPG</t>
         </is>
       </c>
       <c r="B57" t="n">
-        <v>0.052597</v>
+        <v>0.026461</v>
       </c>
       <c r="C57" t="n">
-        <v>0.024562</v>
+        <v>0.015661</v>
       </c>
       <c r="D57" t="n">
-        <v>0.010851</v>
+        <v>0.025313</v>
       </c>
       <c r="E57" t="n">
-        <v>0.03387</v>
+        <v>0.043945</v>
       </c>
       <c r="F57" t="n">
-        <v>0.035563</v>
+        <v>0.066535</v>
       </c>
     </row>
     <row r="58">
       <c r="A58" t="inlineStr">
         <is>
-          <t>FA0057</t>
+          <t>1.对称轴133张/程瑞霖.JPG</t>
         </is>
       </c>
       <c r="B58" t="n">
-        <v>0.019582</v>
+        <v>0.026803</v>
       </c>
       <c r="C58" t="n">
-        <v>0.026077</v>
+        <v>0.026436</v>
       </c>
       <c r="D58" t="n">
-        <v>0.01853</v>
+        <v>0.016959</v>
       </c>
       <c r="E58" t="n">
-        <v>0.023833</v>
+        <v>0.036459</v>
       </c>
       <c r="F58" t="n">
-        <v>0.039251</v>
+        <v>0.071287</v>
       </c>
     </row>
     <row r="59">
       <c r="A59" t="inlineStr">
         <is>
-          <t>FA0058</t>
+          <t>1.对称轴133张/范琳玉.JPG</t>
         </is>
       </c>
       <c r="B59" t="n">
-        <v>0.030471</v>
+        <v>0.031377</v>
       </c>
       <c r="C59" t="n">
-        <v>0.021258</v>
+        <v>0.014972</v>
       </c>
       <c r="D59" t="n">
-        <v>0.028643</v>
+        <v>0.005528</v>
       </c>
       <c r="E59" t="n">
-        <v>0.013817</v>
+        <v>0.017533</v>
       </c>
       <c r="F59" t="n">
-        <v>0.028852</v>
+        <v>0.051206</v>
       </c>
     </row>
     <row r="60">
       <c r="A60" t="inlineStr">
         <is>
-          <t>FA0059</t>
+          <t>1.对称轴133张/范皖皖.JPG</t>
         </is>
       </c>
       <c r="B60" t="n">
-        <v>0.027935</v>
+        <v>0.029331</v>
       </c>
       <c r="C60" t="n">
-        <v>0.028012</v>
+        <v>0.013071</v>
       </c>
       <c r="D60" t="n">
-        <v>0.008260999999999999</v>
+        <v>0.039801</v>
       </c>
       <c r="E60" t="n">
-        <v>0.01219</v>
+        <v>0.027688</v>
       </c>
       <c r="F60" t="n">
-        <v>0.034416</v>
+        <v>0.07495300000000001</v>
       </c>
     </row>
     <row r="61">
       <c r="A61" t="inlineStr">
         <is>
-          <t>FA0060</t>
+          <t>1.对称轴133张/董何鑫.JPG</t>
         </is>
       </c>
       <c r="B61" t="n">
-        <v>0.021171</v>
+        <v>0.010442</v>
       </c>
       <c r="C61" t="n">
-        <v>0.018911</v>
+        <v>0.010572</v>
       </c>
       <c r="D61" t="n">
-        <v>0.008924</v>
+        <v>0.010549</v>
       </c>
       <c r="E61" t="n">
-        <v>0.034928</v>
+        <v>0.034583</v>
       </c>
       <c r="F61" t="n">
-        <v>0.045884</v>
+        <v>0.0649</v>
       </c>
     </row>
     <row r="62">
       <c r="A62" t="inlineStr">
         <is>
-          <t>FA0061</t>
+          <t>1.对称轴133张/董芮君.JPG</t>
         </is>
       </c>
       <c r="B62" t="n">
-        <v>0.042095</v>
+        <v>0.021531</v>
       </c>
       <c r="C62" t="n">
-        <v>0.041995</v>
+        <v>0.009931000000000001</v>
       </c>
       <c r="D62" t="n">
-        <v>0.010454</v>
+        <v>0.019026</v>
       </c>
       <c r="E62" t="n">
-        <v>0.015117</v>
+        <v>0.016936</v>
       </c>
       <c r="F62" t="n">
-        <v>0.016275</v>
+        <v>0.037673</v>
       </c>
     </row>
     <row r="63">
       <c r="A63" t="inlineStr">
         <is>
-          <t>FA0062</t>
+          <t>1.对称轴133张/董英涵.JPG</t>
         </is>
       </c>
       <c r="B63" t="n">
-        <v>0.049813</v>
+        <v>0.014562</v>
       </c>
       <c r="C63" t="n">
-        <v>0.033586</v>
+        <v>0.018623</v>
       </c>
       <c r="D63" t="n">
-        <v>0.033724</v>
+        <v>0.047446</v>
       </c>
       <c r="E63" t="n">
-        <v>0.03027</v>
+        <v>0.049921</v>
       </c>
       <c r="F63" t="n">
-        <v>0.023049</v>
+        <v>0.108187</v>
       </c>
     </row>
     <row r="64">
       <c r="A64" t="inlineStr">
         <is>
-          <t>FA0063</t>
+          <t>1.对称轴133张/蔡修杰.JPG</t>
         </is>
       </c>
       <c r="B64" t="n">
-        <v>0.049501</v>
+        <v>0.028959</v>
       </c>
       <c r="C64" t="n">
-        <v>0.024121</v>
+        <v>0.01747</v>
       </c>
       <c r="D64" t="n">
-        <v>0.017372</v>
+        <v>0.015545</v>
       </c>
       <c r="E64" t="n">
-        <v>0.020973</v>
+        <v>0.009048</v>
       </c>
       <c r="F64" t="n">
-        <v>0.006263</v>
+        <v>0.054593</v>
       </c>
     </row>
     <row r="65">
       <c r="A65" t="inlineStr">
         <is>
-          <t>FA0064</t>
+          <t>1.对称轴133张/蔡艳红.JPG</t>
         </is>
       </c>
       <c r="B65" t="n">
-        <v>0.025135</v>
+        <v>0.028671</v>
       </c>
       <c r="C65" t="n">
-        <v>0.028553</v>
+        <v>0.011735</v>
       </c>
       <c r="D65" t="n">
-        <v>0.013593</v>
+        <v>0.018794</v>
       </c>
       <c r="E65" t="n">
-        <v>0.021261</v>
+        <v>0.046939</v>
       </c>
       <c r="F65" t="n">
-        <v>0.025515</v>
+        <v>0.08792</v>
       </c>
     </row>
     <row r="66">
       <c r="A66" t="inlineStr">
         <is>
-          <t>FA0065</t>
+          <t>1.对称轴133张/蔡芊.JPG</t>
         </is>
       </c>
       <c r="B66" t="n">
-        <v>0.03002</v>
+        <v>0.020531</v>
       </c>
       <c r="C66" t="n">
-        <v>0.012299</v>
+        <v>0.017441</v>
       </c>
       <c r="D66" t="n">
-        <v>0.003841</v>
+        <v>0.027933</v>
       </c>
       <c r="E66" t="n">
-        <v>0.041764</v>
+        <v>0.027665</v>
       </c>
       <c r="F66" t="n">
-        <v>0.050006</v>
+        <v>0.064695</v>
       </c>
     </row>
     <row r="67">
       <c r="A67" t="inlineStr">
         <is>
-          <t>FA0066</t>
+          <t>1.对称轴133张/蔡芸阳.JPG</t>
         </is>
       </c>
       <c r="B67" t="n">
-        <v>0.034122</v>
+        <v>0.020905</v>
       </c>
       <c r="C67" t="n">
-        <v>0.021288</v>
+        <v>0.013577</v>
       </c>
       <c r="D67" t="n">
-        <v>0.011382</v>
+        <v>0.020625</v>
       </c>
       <c r="E67" t="n">
-        <v>0.018121</v>
+        <v>0.016665</v>
       </c>
       <c r="F67" t="n">
-        <v>0.058462</v>
+        <v>0.03522</v>
       </c>
     </row>
     <row r="68">
       <c r="A68" t="inlineStr">
         <is>
-          <t>FA0067</t>
+          <t>1.对称轴133张/邓乔月.JPG</t>
         </is>
       </c>
       <c r="B68" t="n">
-        <v>0.095585</v>
+        <v>0.024119</v>
       </c>
       <c r="C68" t="n">
-        <v>0.08007300000000001</v>
+        <v>0.01429</v>
       </c>
       <c r="D68" t="n">
-        <v>0.011786</v>
+        <v>0.004882</v>
       </c>
       <c r="E68" t="n">
-        <v>0.02161</v>
+        <v>0.038612</v>
       </c>
       <c r="F68" t="n">
-        <v>0.022636</v>
+        <v>0.029096</v>
       </c>
     </row>
     <row r="69">
       <c r="A69" t="inlineStr">
         <is>
-          <t>FA0068</t>
+          <t>1.对称轴133张/邓力恒.JPG</t>
         </is>
       </c>
       <c r="B69" t="n">
-        <v>0.021196</v>
+        <v>0.020842</v>
       </c>
       <c r="C69" t="n">
-        <v>0.021506</v>
+        <v>0.013254</v>
       </c>
       <c r="D69" t="n">
-        <v>0.025068</v>
+        <v>0.02634</v>
       </c>
       <c r="E69" t="n">
-        <v>0.043664</v>
+        <v>0.031417</v>
       </c>
       <c r="F69" t="n">
-        <v>0.069981</v>
+        <v>0.08164299999999999</v>
       </c>
     </row>
     <row r="70">
       <c r="A70" t="inlineStr">
         <is>
-          <t>FA0069</t>
+          <t>1.对称轴133张/邓墨苒.JPG</t>
         </is>
       </c>
       <c r="B70" t="n">
-        <v>0.031864</v>
+        <v>0.032099</v>
       </c>
       <c r="C70" t="n">
-        <v>0.027956</v>
+        <v>0.025532</v>
       </c>
       <c r="D70" t="n">
-        <v>0.013358</v>
+        <v>0.042635</v>
       </c>
       <c r="E70" t="n">
-        <v>0.028088</v>
+        <v>0.042999</v>
       </c>
       <c r="F70" t="n">
-        <v>0.030989</v>
+        <v>0.059357</v>
       </c>
     </row>
     <row r="71">
       <c r="A71" t="inlineStr">
         <is>
-          <t>FA0070</t>
+          <t>1.对称轴133张/邓必红.JPG</t>
         </is>
       </c>
       <c r="B71" t="n">
-        <v>0.033657</v>
+        <v>0.035063</v>
       </c>
       <c r="C71" t="n">
-        <v>0.023046</v>
+        <v>0.013205</v>
       </c>
       <c r="D71" t="n">
-        <v>0.059699</v>
+        <v>0.016299</v>
       </c>
       <c r="E71" t="n">
-        <v>0.044365</v>
+        <v>0.023042</v>
       </c>
       <c r="F71" t="n">
-        <v>0.036874</v>
+        <v>0.083202</v>
       </c>
     </row>
     <row r="72">
       <c r="A72" t="inlineStr">
         <is>
-          <t>FA0071</t>
+          <t>1.对称轴133张/邓悦兴.JPG</t>
         </is>
       </c>
       <c r="B72" t="n">
-        <v>0.025874</v>
+        <v>0.03803</v>
       </c>
       <c r="C72" t="n">
-        <v>0.019595</v>
+        <v>0.01041</v>
       </c>
       <c r="D72" t="n">
-        <v>0.037678</v>
+        <v>0.026693</v>
       </c>
       <c r="E72" t="n">
-        <v>0.040617</v>
+        <v>0.025596</v>
       </c>
       <c r="F72" t="n">
-        <v>0.09930700000000001</v>
+        <v>0.030509</v>
       </c>
     </row>
     <row r="73">
       <c r="A73" t="inlineStr">
         <is>
-          <t>FA0072</t>
+          <t>1.对称轴133张/邓文慧.JPG</t>
         </is>
       </c>
       <c r="B73" t="n">
-        <v>0.039277</v>
+        <v>0.019018</v>
       </c>
       <c r="C73" t="n">
-        <v>0.021779</v>
+        <v>0.011017</v>
       </c>
       <c r="D73" t="n">
-        <v>0.028917</v>
+        <v>0.040027</v>
       </c>
       <c r="E73" t="n">
-        <v>0.020268</v>
+        <v>0.006556</v>
       </c>
       <c r="F73" t="n">
-        <v>0.045529</v>
+        <v>0.034384</v>
       </c>
     </row>
     <row r="74">
       <c r="A74" t="inlineStr">
         <is>
-          <t>FA0073</t>
+          <t>1.对称轴133张/邓洋洋.JPG</t>
         </is>
       </c>
       <c r="B74" t="n">
-        <v>0.022925</v>
+        <v>0.03639</v>
       </c>
       <c r="C74" t="n">
-        <v>0.012793</v>
+        <v>0.01627</v>
       </c>
       <c r="D74" t="n">
-        <v>0.010287</v>
+        <v>0.02453</v>
       </c>
       <c r="E74" t="n">
-        <v>0.031069</v>
+        <v>0.020153</v>
       </c>
       <c r="F74" t="n">
-        <v>0.050643</v>
+        <v>0.025444</v>
       </c>
     </row>
     <row r="75">
       <c r="A75" t="inlineStr">
         <is>
-          <t>FA0074</t>
+          <t>1.对称轴133张/邓雨宸.JPG</t>
         </is>
       </c>
       <c r="B75" t="n">
-        <v>0.027108</v>
+        <v>0.017529</v>
       </c>
       <c r="C75" t="n">
-        <v>0.026361</v>
+        <v>0.008309</v>
       </c>
       <c r="D75" t="n">
-        <v>0.020169</v>
+        <v>0.008546</v>
       </c>
       <c r="E75" t="n">
-        <v>0.0105</v>
+        <v>0.017334</v>
       </c>
       <c r="F75" t="n">
-        <v>0.062571</v>
+        <v>0.043486</v>
       </c>
     </row>
     <row r="76">
       <c r="A76" t="inlineStr">
         <is>
-          <t>FA0075</t>
+          <t>1.对称轴133张/邓雪.JPG</t>
         </is>
       </c>
       <c r="B76" t="n">
-        <v>0.050388</v>
+        <v>0.034403</v>
       </c>
       <c r="C76" t="n">
-        <v>0.040153</v>
+        <v>0.018145</v>
       </c>
       <c r="D76" t="n">
-        <v>0.007269</v>
+        <v>0.013615</v>
       </c>
       <c r="E76" t="n">
-        <v>0.037773</v>
+        <v>0.030556</v>
       </c>
       <c r="F76" t="n">
-        <v>0.015722</v>
+        <v>0.022935</v>
       </c>
     </row>
     <row r="77">
       <c r="A77" t="inlineStr">
         <is>
-          <t>FA0076</t>
+          <t>1.对称轴133张/都涵睿.JPG</t>
         </is>
       </c>
       <c r="B77" t="n">
-        <v>0.049895</v>
+        <v>0.023529</v>
       </c>
       <c r="C77" t="n">
-        <v>0.023828</v>
+        <v>0.018934</v>
       </c>
       <c r="D77" t="n">
-        <v>0.016851</v>
+        <v>0.002277</v>
       </c>
       <c r="E77" t="n">
-        <v>0.040425</v>
+        <v>0.0414</v>
       </c>
       <c r="F77" t="n">
-        <v>0.097387</v>
+        <v>0.061398</v>
       </c>
     </row>
     <row r="78">
       <c r="A78" t="inlineStr">
         <is>
-          <t>FA0077</t>
+          <t>1.对称轴133张/阿依晓芳.JPG</t>
         </is>
       </c>
       <c r="B78" t="n">
-        <v>0.031637</v>
+        <v>0.031625</v>
       </c>
       <c r="C78" t="n">
-        <v>0.02848</v>
+        <v>0.019991</v>
       </c>
       <c r="D78" t="n">
-        <v>0.059613</v>
+        <v>0.036239</v>
       </c>
       <c r="E78" t="n">
-        <v>0.071025</v>
+        <v>0.052302</v>
       </c>
       <c r="F78" t="n">
-        <v>0.104638</v>
+        <v>0.076499</v>
       </c>
     </row>
     <row r="79">
       <c r="A79" t="inlineStr">
         <is>
-          <t>FA0078</t>
+          <t>1.对称轴133张/陈丽.JPG</t>
         </is>
       </c>
       <c r="B79" t="n">
-        <v>0.033949</v>
+        <v>0.025022</v>
       </c>
       <c r="C79" t="n">
-        <v>0.019612</v>
+        <v>0.023334</v>
       </c>
       <c r="D79" t="n">
-        <v>0.030472</v>
+        <v>0.048035</v>
       </c>
       <c r="E79" t="n">
-        <v>0.053064</v>
+        <v>0.053525</v>
       </c>
       <c r="F79" t="n">
-        <v>0.056554</v>
+        <v>0.102345</v>
       </c>
     </row>
     <row r="80">
       <c r="A80" t="inlineStr">
         <is>
-          <t>FA0079</t>
+          <t>1.对称轴133张/陈伟.JPG</t>
         </is>
       </c>
       <c r="B80" t="n">
-        <v>0.033527</v>
+        <v>0.035547</v>
       </c>
       <c r="C80" t="n">
-        <v>0.011203</v>
+        <v>0.014661</v>
       </c>
       <c r="D80" t="n">
-        <v>0.006354</v>
+        <v>0.014717</v>
       </c>
       <c r="E80" t="n">
-        <v>0.026386</v>
+        <v>0.044074</v>
       </c>
       <c r="F80" t="n">
-        <v>0.051351</v>
+        <v>0.101869</v>
       </c>
     </row>
     <row r="81">
       <c r="A81" t="inlineStr">
         <is>
-          <t>FA0080</t>
+          <t>1.对称轴133张/陈佳倩.JPG</t>
         </is>
       </c>
       <c r="B81" t="n">
-        <v>0.025951</v>
+        <v>0.019646</v>
       </c>
       <c r="C81" t="n">
-        <v>0.027143</v>
+        <v>0.008727</v>
       </c>
       <c r="D81" t="n">
-        <v>0.024278</v>
+        <v>0.0148</v>
       </c>
       <c r="E81" t="n">
-        <v>0.018756</v>
+        <v>0.020824</v>
       </c>
       <c r="F81" t="n">
-        <v>0.037084</v>
+        <v>0.06948600000000001</v>
       </c>
     </row>
     <row r="82">
       <c r="A82" t="inlineStr">
         <is>
-          <t>FA0081</t>
+          <t>1.对称轴133张/陈俊.JPG</t>
         </is>
       </c>
       <c r="B82" t="n">
-        <v>0.051089</v>
+        <v>0.025995</v>
       </c>
       <c r="C82" t="n">
-        <v>0.029313</v>
+        <v>0.017957</v>
       </c>
       <c r="D82" t="n">
-        <v>0.010325</v>
+        <v>0.007394</v>
       </c>
       <c r="E82" t="n">
-        <v>0.021427</v>
+        <v>0.018476</v>
       </c>
       <c r="F82" t="n">
-        <v>0.059633</v>
+        <v>0.027132</v>
       </c>
     </row>
     <row r="83">
       <c r="A83" t="inlineStr">
         <is>
-          <t>FA0082</t>
+          <t>1.对称轴133张/陈兴烨.JPG</t>
         </is>
       </c>
       <c r="B83" t="n">
-        <v>0.027271</v>
+        <v>0.029316</v>
       </c>
       <c r="C83" t="n">
-        <v>0.016449</v>
+        <v>0.019276</v>
       </c>
       <c r="D83" t="n">
-        <v>0.033895</v>
+        <v>0.018367</v>
       </c>
       <c r="E83" t="n">
-        <v>0.014948</v>
+        <v>0.016905</v>
       </c>
       <c r="F83" t="n">
-        <v>0.003416</v>
+        <v>0.054647</v>
       </c>
     </row>
     <row r="84">
       <c r="A84" t="inlineStr">
         <is>
-          <t>FA0083</t>
+          <t>1.对称轴133张/陈冠宇.JPG</t>
         </is>
       </c>
       <c r="B84" t="n">
-        <v>0.051041</v>
+        <v>0.019688</v>
       </c>
       <c r="C84" t="n">
-        <v>0.033042</v>
+        <v>0.009205</v>
       </c>
       <c r="D84" t="n">
-        <v>0.02283</v>
+        <v>0.008829</v>
       </c>
       <c r="E84" t="n">
-        <v>0.032061</v>
+        <v>0.013954</v>
       </c>
       <c r="F84" t="n">
-        <v>0.039552</v>
+        <v>0.03076</v>
       </c>
     </row>
     <row r="85">
       <c r="A85" t="inlineStr">
         <is>
-          <t>FA0084</t>
+          <t>1.对称轴133张/陈发扬.JPG</t>
         </is>
       </c>
       <c r="B85" t="n">
-        <v>0.034884</v>
+        <v>0.023463</v>
       </c>
       <c r="C85" t="n">
-        <v>0.02717</v>
+        <v>0.022963</v>
       </c>
       <c r="D85" t="n">
-        <v>0.027082</v>
+        <v>0.025521</v>
       </c>
       <c r="E85" t="n">
-        <v>0.027409</v>
+        <v>0.037879</v>
       </c>
       <c r="F85" t="n">
-        <v>0.009580999999999999</v>
+        <v>0.023996</v>
       </c>
     </row>
     <row r="86">
       <c r="A86" t="inlineStr">
         <is>
-          <t>FA0085</t>
+          <t>1.对称轴133张/陈嘉伟.JPG</t>
         </is>
       </c>
       <c r="B86" t="n">
-        <v>0.018645</v>
+        <v>0.014798</v>
       </c>
       <c r="C86" t="n">
-        <v>0.008559000000000001</v>
+        <v>0.016127</v>
       </c>
       <c r="D86" t="n">
-        <v>0.018092</v>
+        <v>0.008746</v>
       </c>
       <c r="E86" t="n">
-        <v>0.012592</v>
+        <v>0.028796</v>
       </c>
       <c r="F86" t="n">
-        <v>0.016688</v>
+        <v>0.049351</v>
       </c>
     </row>
     <row r="87">
       <c r="A87" t="inlineStr">
         <is>
-          <t>FA0086</t>
+          <t>1.对称轴133张/陈垚舟.JPG</t>
         </is>
       </c>
       <c r="B87" t="n">
-        <v>0.056121</v>
+        <v>0.020019</v>
       </c>
       <c r="C87" t="n">
-        <v>0.009159</v>
+        <v>0.016629</v>
       </c>
       <c r="D87" t="n">
-        <v>0.031335</v>
+        <v>0.008214000000000001</v>
       </c>
       <c r="E87" t="n">
-        <v>0.035798</v>
+        <v>0.020554</v>
       </c>
       <c r="F87" t="n">
-        <v>0.06516</v>
+        <v>0.05358</v>
       </c>
     </row>
     <row r="88">
       <c r="A88" t="inlineStr">
         <is>
-          <t>FA0087</t>
+          <t>1.对称轴133张/陈娟.JPG</t>
         </is>
       </c>
       <c r="B88" t="n">
-        <v>0.043872</v>
+        <v>0.025276</v>
       </c>
       <c r="C88" t="n">
-        <v>0.006079</v>
+        <v>0.008678</v>
       </c>
       <c r="D88" t="n">
-        <v>0.032507</v>
+        <v>0.017512</v>
       </c>
       <c r="E88" t="n">
-        <v>0.025672</v>
+        <v>0.036248</v>
       </c>
       <c r="F88" t="n">
-        <v>0.068324</v>
+        <v>0.054891</v>
       </c>
     </row>
     <row r="89">
       <c r="A89" t="inlineStr">
         <is>
-          <t>FA0088</t>
+          <t>1.对称轴133张/陈婕.JPG</t>
         </is>
       </c>
       <c r="B89" t="n">
-        <v>0.028447</v>
+        <v>0.017507</v>
       </c>
       <c r="C89" t="n">
-        <v>0.01154</v>
+        <v>0.011232</v>
       </c>
       <c r="D89" t="n">
-        <v>0.025212</v>
+        <v>0.018869</v>
       </c>
       <c r="E89" t="n">
-        <v>0.029991</v>
+        <v>0.060035</v>
       </c>
       <c r="F89" t="n">
-        <v>0.06393699999999999</v>
+        <v>0.087922</v>
       </c>
     </row>
     <row r="90">
       <c r="A90" t="inlineStr">
         <is>
-          <t>FA0089</t>
+          <t>1.对称轴133张/陈婷.JPG</t>
         </is>
       </c>
       <c r="B90" t="n">
-        <v>0.028332</v>
+        <v>0.018705</v>
       </c>
       <c r="C90" t="n">
-        <v>0.007045</v>
+        <v>0.016062</v>
       </c>
       <c r="D90" t="n">
-        <v>0.015355</v>
+        <v>0.028226</v>
       </c>
       <c r="E90" t="n">
-        <v>0.018747</v>
+        <v>0.048516</v>
       </c>
       <c r="F90" t="n">
-        <v>0.046967</v>
+        <v>0.056094</v>
       </c>
     </row>
     <row r="91">
       <c r="A91" t="inlineStr">
         <is>
-          <t>FA0090</t>
+          <t>1.对称轴133张/陈嫣然.JPG</t>
         </is>
       </c>
       <c r="B91" t="n">
-        <v>0.02331</v>
+        <v>0.020529</v>
       </c>
       <c r="C91" t="n">
-        <v>0.013019</v>
+        <v>0.040507</v>
       </c>
       <c r="D91" t="n">
-        <v>0.036084</v>
+        <v>0.006289</v>
       </c>
       <c r="E91" t="n">
-        <v>0.046509</v>
+        <v>0.02451</v>
       </c>
       <c r="F91" t="n">
-        <v>0.132911</v>
+        <v>0.117681</v>
       </c>
     </row>
     <row r="92">
       <c r="A92" t="inlineStr">
         <is>
-          <t>FA0091</t>
+          <t>1.对称轴133张/陈子墨.JPG</t>
         </is>
       </c>
       <c r="B92" t="n">
-        <v>0.026656</v>
+        <v>0.024801</v>
       </c>
       <c r="C92" t="n">
-        <v>0.019288</v>
+        <v>0.009674</v>
       </c>
       <c r="D92" t="n">
-        <v>0.027394</v>
+        <v>0.005665</v>
       </c>
       <c r="E92" t="n">
-        <v>0.036691</v>
+        <v>0.019808</v>
       </c>
       <c r="F92" t="n">
-        <v>0.037906</v>
+        <v>0.068679</v>
       </c>
     </row>
     <row r="93">
       <c r="A93" t="inlineStr">
         <is>
-          <t>FA0092</t>
+          <t>1.对称轴133张/陈子攸.JPG</t>
         </is>
       </c>
       <c r="B93" t="n">
-        <v>0.047768</v>
+        <v>0.026207</v>
       </c>
       <c r="C93" t="n">
-        <v>0.012646</v>
+        <v>0.019056</v>
       </c>
       <c r="D93" t="n">
-        <v>0.042104</v>
+        <v>0.017867</v>
       </c>
       <c r="E93" t="n">
-        <v>0.031407</v>
+        <v>0.037182</v>
       </c>
       <c r="F93" t="n">
-        <v>0.05533</v>
+        <v>0.019894</v>
       </c>
     </row>
     <row r="94">
       <c r="A94" t="inlineStr">
         <is>
-          <t>FA0093</t>
+          <t>1.对称轴133张/陈宇佳.JPG</t>
         </is>
       </c>
       <c r="B94" t="n">
-        <v>0.019453</v>
+        <v>0.037028</v>
       </c>
       <c r="C94" t="n">
-        <v>0.018776</v>
+        <v>0.015618</v>
       </c>
       <c r="D94" t="n">
-        <v>0.00764</v>
+        <v>0.044958</v>
       </c>
       <c r="E94" t="n">
-        <v>0.015828</v>
+        <v>0.04987</v>
       </c>
       <c r="F94" t="n">
-        <v>0.094691</v>
+        <v>0.06253599999999999</v>
       </c>
     </row>
     <row r="95">
       <c r="A95" t="inlineStr">
         <is>
-          <t>FA0094</t>
+          <t>1.对称轴133张/陈宇凡.JPG</t>
         </is>
       </c>
       <c r="B95" t="n">
-        <v>0.029956</v>
+        <v>0.030517</v>
       </c>
       <c r="C95" t="n">
-        <v>0.012331</v>
+        <v>0.015743</v>
       </c>
       <c r="D95" t="n">
-        <v>0.019818</v>
+        <v>0.019883</v>
       </c>
       <c r="E95" t="n">
-        <v>0.010124</v>
+        <v>0.004958</v>
       </c>
       <c r="F95" t="n">
-        <v>0.021609</v>
+        <v>0.007219</v>
       </c>
     </row>
     <row r="96">
       <c r="A96" t="inlineStr">
         <is>
-          <t>FA0095</t>
+          <t>1.对称轴133张/陈宇博.JPG</t>
         </is>
       </c>
       <c r="B96" t="n">
-        <v>0.050387</v>
+        <v>0.030163</v>
       </c>
       <c r="C96" t="n">
-        <v>0.018805</v>
+        <v>0.016165</v>
       </c>
       <c r="D96" t="n">
-        <v>0.014028</v>
+        <v>0.054884</v>
       </c>
       <c r="E96" t="n">
-        <v>0.057341</v>
+        <v>0.07370599999999999</v>
       </c>
       <c r="F96" t="n">
-        <v>0.036037</v>
+        <v>0.147804</v>
       </c>
     </row>
     <row r="97">
       <c r="A97" t="inlineStr">
         <is>
-          <t>FA0096</t>
+          <t>1.对称轴133张/陈安静.JPG</t>
         </is>
       </c>
       <c r="B97" t="n">
-        <v>0.026773</v>
+        <v>0.025823</v>
       </c>
       <c r="C97" t="n">
-        <v>0.019973</v>
+        <v>0.013121</v>
       </c>
       <c r="D97" t="n">
-        <v>0.038986</v>
+        <v>0.028684</v>
       </c>
       <c r="E97" t="n">
-        <v>0.055364</v>
+        <v>0.01356</v>
       </c>
       <c r="F97" t="n">
-        <v>0.090419</v>
+        <v>0.052919</v>
       </c>
     </row>
     <row r="98">
       <c r="A98" t="inlineStr">
         <is>
-          <t>FA0097</t>
+          <t>1.对称轴133张/陈小洪.JPG</t>
         </is>
       </c>
       <c r="B98" t="n">
-        <v>0.028981</v>
+        <v>0.044234</v>
       </c>
       <c r="C98" t="n">
-        <v>0.033306</v>
+        <v>0.025146</v>
       </c>
       <c r="D98" t="n">
-        <v>0.012282</v>
+        <v>0.049916</v>
       </c>
       <c r="E98" t="n">
-        <v>0.045749</v>
+        <v>0.048254</v>
       </c>
       <c r="F98" t="n">
-        <v>0.049264</v>
+        <v>0.064348</v>
       </c>
     </row>
     <row r="99">
       <c r="A99" t="inlineStr">
         <is>
-          <t>FA0098</t>
+          <t>1.对称轴133张/陈尧.JPG</t>
         </is>
       </c>
       <c r="B99" t="n">
-        <v>0.018466</v>
+        <v>0.019103</v>
       </c>
       <c r="C99" t="n">
-        <v>0.022807</v>
+        <v>0.018048</v>
       </c>
       <c r="D99" t="n">
-        <v>0.004192</v>
+        <v>0.008969</v>
       </c>
       <c r="E99" t="n">
-        <v>0.027089</v>
+        <v>0.012244</v>
       </c>
       <c r="F99" t="n">
-        <v>0.079112</v>
+        <v>0.03897</v>
       </c>
     </row>
     <row r="100">
       <c r="A100" t="inlineStr">
         <is>
-          <t>FA0099</t>
+          <t>1.对称轴133张/陈庆敏.JPG</t>
         </is>
       </c>
       <c r="B100" t="n">
-        <v>0.037049</v>
+        <v>0.021096</v>
       </c>
       <c r="C100" t="n">
-        <v>0.039099</v>
+        <v>0.019782</v>
       </c>
       <c r="D100" t="n">
-        <v>0.011794</v>
+        <v>0.022285</v>
       </c>
       <c r="E100" t="n">
-        <v>0.010804</v>
+        <v>0.023721</v>
       </c>
       <c r="F100" t="n">
-        <v>0.039056</v>
+        <v>0.008914999999999999</v>
       </c>
     </row>
     <row r="101">
       <c r="A101" t="inlineStr">
         <is>
-          <t>FA0100</t>
+          <t>1.对称轴133张/陈志飞.JPG</t>
         </is>
       </c>
       <c r="B101" t="n">
-        <v>0.043285</v>
+        <v>0.054919</v>
       </c>
       <c r="C101" t="n">
-        <v>0.032163</v>
+        <v>0.013714</v>
       </c>
       <c r="D101" t="n">
-        <v>0.030187</v>
+        <v>0.034987</v>
       </c>
       <c r="E101" t="n">
-        <v>0.038858</v>
+        <v>0.045152</v>
       </c>
       <c r="F101" t="n">
-        <v>0.019952</v>
+        <v>0.01571</v>
+      </c>
+    </row>
+    <row r="102">
+      <c r="A102" t="inlineStr">
+        <is>
+          <t>1.对称轴133张/陈思.JPG</t>
+        </is>
+      </c>
+      <c r="B102" t="n">
+        <v>0.02837</v>
+      </c>
+      <c r="C102" t="n">
+        <v>0.012486</v>
+      </c>
+      <c r="D102" t="n">
+        <v>0.020629</v>
+      </c>
+      <c r="E102" t="n">
+        <v>0.010925</v>
+      </c>
+      <c r="F102" t="n">
+        <v>0.020593</v>
+      </c>
+    </row>
+    <row r="103">
+      <c r="A103" t="inlineStr">
+        <is>
+          <t>1.对称轴133张/陈思源.JPG</t>
+        </is>
+      </c>
+      <c r="B103" t="n">
+        <v>0.026017</v>
+      </c>
+      <c r="C103" t="n">
+        <v>0.025107</v>
+      </c>
+      <c r="D103" t="n">
+        <v>0.025263</v>
+      </c>
+      <c r="E103" t="n">
+        <v>0.041556</v>
+      </c>
+      <c r="F103" t="n">
+        <v>0.127597</v>
+      </c>
+    </row>
+    <row r="104">
+      <c r="A104" t="inlineStr">
+        <is>
+          <t>1.对称轴133张/陈怡洁.JPG</t>
+        </is>
+      </c>
+      <c r="B104" t="n">
+        <v>0.045034</v>
+      </c>
+      <c r="C104" t="n">
+        <v>0.022899</v>
+      </c>
+      <c r="D104" t="n">
+        <v>0.028771</v>
+      </c>
+      <c r="E104" t="n">
+        <v>0.038728</v>
+      </c>
+      <c r="F104" t="n">
+        <v>0.011286</v>
+      </c>
+    </row>
+    <row r="105">
+      <c r="A105" t="inlineStr">
+        <is>
+          <t>1.对称轴133张/陈悦.JPG</t>
+        </is>
+      </c>
+      <c r="B105" t="n">
+        <v>0.03492</v>
+      </c>
+      <c r="C105" t="n">
+        <v>0.008288999999999999</v>
+      </c>
+      <c r="D105" t="n">
+        <v>0.023093</v>
+      </c>
+      <c r="E105" t="n">
+        <v>0.010843</v>
+      </c>
+      <c r="F105" t="n">
+        <v>0.027571</v>
+      </c>
+    </row>
+    <row r="106">
+      <c r="A106" t="inlineStr">
+        <is>
+          <t>1.对称轴133张/陈惠.JPG</t>
+        </is>
+      </c>
+      <c r="B106" t="n">
+        <v>0.02566</v>
+      </c>
+      <c r="C106" t="n">
+        <v>0.005143</v>
+      </c>
+      <c r="D106" t="n">
+        <v>0.040065</v>
+      </c>
+      <c r="E106" t="n">
+        <v>0.013359</v>
+      </c>
+      <c r="F106" t="n">
+        <v>0.049966</v>
+      </c>
+    </row>
+    <row r="107">
+      <c r="A107" t="inlineStr">
+        <is>
+          <t>1.对称轴133张/陈意婕.JPG</t>
+        </is>
+      </c>
+      <c r="B107" t="n">
+        <v>0.016438</v>
+      </c>
+      <c r="C107" t="n">
+        <v>0.019825</v>
+      </c>
+      <c r="D107" t="n">
+        <v>0.038299</v>
+      </c>
+      <c r="E107" t="n">
+        <v>0.042541</v>
+      </c>
+      <c r="F107" t="n">
+        <v>0.124263</v>
+      </c>
+    </row>
+    <row r="108">
+      <c r="A108" t="inlineStr">
+        <is>
+          <t>1.对称轴133张/陈曹瑞.JPG</t>
+        </is>
+      </c>
+      <c r="B108" t="n">
+        <v>0.029555</v>
+      </c>
+      <c r="C108" t="n">
+        <v>0.019936</v>
+      </c>
+      <c r="D108" t="n">
+        <v>0.006912</v>
+      </c>
+      <c r="E108" t="n">
+        <v>0.027531</v>
+      </c>
+      <c r="F108" t="n">
+        <v>0.008716</v>
+      </c>
+    </row>
+    <row r="109">
+      <c r="A109" t="inlineStr">
+        <is>
+          <t>1.对称轴133张/陈有谋.JPG</t>
+        </is>
+      </c>
+      <c r="B109" t="n">
+        <v>0.014933</v>
+      </c>
+      <c r="C109" t="n">
+        <v>0.007937</v>
+      </c>
+      <c r="D109" t="n">
+        <v>0.014266</v>
+      </c>
+      <c r="E109" t="n">
+        <v>0.00954</v>
+      </c>
+      <c r="F109" t="n">
+        <v>0.007087</v>
+      </c>
+    </row>
+    <row r="110">
+      <c r="A110" t="inlineStr">
+        <is>
+          <t>1.对称轴133张/陈朴阳.JPG</t>
+        </is>
+      </c>
+      <c r="B110" t="n">
+        <v>0.040324</v>
+      </c>
+      <c r="C110" t="n">
+        <v>0.039543</v>
+      </c>
+      <c r="D110" t="n">
+        <v>0.007705</v>
+      </c>
+      <c r="E110" t="n">
+        <v>0.01931</v>
+      </c>
+      <c r="F110" t="n">
+        <v>0.082556</v>
+      </c>
+    </row>
+    <row r="111">
+      <c r="A111" t="inlineStr">
+        <is>
+          <t>1.对称轴133张/陈李睿.JPG</t>
+        </is>
+      </c>
+      <c r="B111" t="n">
+        <v>0.023123</v>
+      </c>
+      <c r="C111" t="n">
+        <v>0.019328</v>
+      </c>
+      <c r="D111" t="n">
+        <v>0.002487</v>
+      </c>
+      <c r="E111" t="n">
+        <v>0.027853</v>
+      </c>
+      <c r="F111" t="n">
+        <v>0.086544</v>
+      </c>
+    </row>
+    <row r="112">
+      <c r="A112" t="inlineStr">
+        <is>
+          <t>1.对称轴133张/陈杰.JPG</t>
+        </is>
+      </c>
+      <c r="B112" t="n">
+        <v>0.021283</v>
+      </c>
+      <c r="C112" t="n">
+        <v>0.013053</v>
+      </c>
+      <c r="D112" t="n">
+        <v>0.010144</v>
+      </c>
+      <c r="E112" t="n">
+        <v>0.029766</v>
+      </c>
+      <c r="F112" t="n">
+        <v>0.06274200000000001</v>
+      </c>
+    </row>
+    <row r="113">
+      <c r="A113" t="inlineStr">
+        <is>
+          <t>1.对称轴133张/陈松毅.JPG</t>
+        </is>
+      </c>
+      <c r="B113" t="n">
+        <v>0.057762</v>
+      </c>
+      <c r="C113" t="n">
+        <v>0.028482</v>
+      </c>
+      <c r="D113" t="n">
+        <v>0.003681</v>
+      </c>
+      <c r="E113" t="n">
+        <v>0.053986</v>
+      </c>
+      <c r="F113" t="n">
+        <v>0.057785</v>
+      </c>
+    </row>
+    <row r="114">
+      <c r="A114" t="inlineStr">
+        <is>
+          <t>1.对称轴133张/陈梦雪.JPG</t>
+        </is>
+      </c>
+      <c r="B114" t="n">
+        <v>0.023221</v>
+      </c>
+      <c r="C114" t="n">
+        <v>0.029874</v>
+      </c>
+      <c r="D114" t="n">
+        <v>0.026805</v>
+      </c>
+      <c r="E114" t="n">
+        <v>0.056553</v>
+      </c>
+      <c r="F114" t="n">
+        <v>0.056133</v>
+      </c>
+    </row>
+    <row r="115">
+      <c r="A115" t="inlineStr">
+        <is>
+          <t>1.对称轴133张/陈欣妍.JPG</t>
+        </is>
+      </c>
+      <c r="B115" t="n">
+        <v>0.030345</v>
+      </c>
+      <c r="C115" t="n">
+        <v>0.01998</v>
+      </c>
+      <c r="D115" t="n">
+        <v>0.01588</v>
+      </c>
+      <c r="E115" t="n">
+        <v>0.016529</v>
+      </c>
+      <c r="F115" t="n">
+        <v>0.030656</v>
+      </c>
+    </row>
+    <row r="116">
+      <c r="A116" t="inlineStr">
+        <is>
+          <t>1.对称轴133张/陈治宇.JPG</t>
+        </is>
+      </c>
+      <c r="B116" t="n">
+        <v>0.029396</v>
+      </c>
+      <c r="C116" t="n">
+        <v>0.021563</v>
+      </c>
+      <c r="D116" t="n">
+        <v>0.012798</v>
+      </c>
+      <c r="E116" t="n">
+        <v>0.028057</v>
+      </c>
+      <c r="F116" t="n">
+        <v>0.032585</v>
+      </c>
+    </row>
+    <row r="117">
+      <c r="A117" t="inlineStr">
+        <is>
+          <t>1.对称轴133张/陈泊桥.JPG</t>
+        </is>
+      </c>
+      <c r="B117" t="n">
+        <v>0.036894</v>
+      </c>
+      <c r="C117" t="n">
+        <v>0.028673</v>
+      </c>
+      <c r="D117" t="n">
+        <v>0.062173</v>
+      </c>
+      <c r="E117" t="n">
+        <v>0.072104</v>
+      </c>
+      <c r="F117" t="n">
+        <v>0.147286</v>
+      </c>
+    </row>
+    <row r="118">
+      <c r="A118" t="inlineStr">
+        <is>
+          <t>1.对称轴133张/陈渔.JPG</t>
+        </is>
+      </c>
+      <c r="B118" t="n">
+        <v>0.021986</v>
+      </c>
+      <c r="C118" t="n">
+        <v>0.019541</v>
+      </c>
+      <c r="D118" t="n">
+        <v>0.010426</v>
+      </c>
+      <c r="E118" t="n">
+        <v>0.014839</v>
+      </c>
+      <c r="F118" t="n">
+        <v>0.027309</v>
+      </c>
+    </row>
+    <row r="119">
+      <c r="A119" t="inlineStr">
+        <is>
+          <t>1.对称轴133张/陈玉婷.JPG</t>
+        </is>
+      </c>
+      <c r="B119" t="n">
+        <v>0.022839</v>
+      </c>
+      <c r="C119" t="n">
+        <v>0.023727</v>
+      </c>
+      <c r="D119" t="n">
+        <v>0.007178</v>
+      </c>
+      <c r="E119" t="n">
+        <v>0.037392</v>
+      </c>
+      <c r="F119" t="n">
+        <v>0.08326</v>
+      </c>
+    </row>
+    <row r="120">
+      <c r="A120" t="inlineStr">
+        <is>
+          <t>1.对称轴133张/陈瑜.JPG</t>
+        </is>
+      </c>
+      <c r="B120" t="n">
+        <v>0.033029</v>
+      </c>
+      <c r="C120" t="n">
+        <v>0.023847</v>
+      </c>
+      <c r="D120" t="n">
+        <v>0.017882</v>
+      </c>
+      <c r="E120" t="n">
+        <v>0.031456</v>
+      </c>
+      <c r="F120" t="n">
+        <v>0.033689</v>
+      </c>
+    </row>
+    <row r="121">
+      <c r="A121" t="inlineStr">
+        <is>
+          <t>1.对称轴133张/陈真.JPG</t>
+        </is>
+      </c>
+      <c r="B121" t="n">
+        <v>0.012667</v>
+      </c>
+      <c r="C121" t="n">
+        <v>0.011083</v>
+      </c>
+      <c r="D121" t="n">
+        <v>0.019047</v>
+      </c>
+      <c r="E121" t="n">
+        <v>0.028261</v>
+      </c>
+      <c r="F121" t="n">
+        <v>0.038387</v>
+      </c>
+    </row>
+    <row r="122">
+      <c r="A122" t="inlineStr">
+        <is>
+          <t>1.对称轴133张/陈米可.JPG</t>
+        </is>
+      </c>
+      <c r="B122" t="n">
+        <v>0.033668</v>
+      </c>
+      <c r="C122" t="n">
+        <v>0.025171</v>
+      </c>
+      <c r="D122" t="n">
+        <v>0.021927</v>
+      </c>
+      <c r="E122" t="n">
+        <v>0.021242</v>
+      </c>
+      <c r="F122" t="n">
+        <v>0.057277</v>
+      </c>
+    </row>
+    <row r="123">
+      <c r="A123" t="inlineStr">
+        <is>
+          <t>1.对称轴133张/陈胤宇.JPG</t>
+        </is>
+      </c>
+      <c r="B123" t="n">
+        <v>0.020837</v>
+      </c>
+      <c r="C123" t="n">
+        <v>0.019345</v>
+      </c>
+      <c r="D123" t="n">
+        <v>0.019998</v>
+      </c>
+      <c r="E123" t="n">
+        <v>0.044176</v>
+      </c>
+      <c r="F123" t="n">
+        <v>0.061667</v>
+      </c>
+    </row>
+    <row r="124">
+      <c r="A124" t="inlineStr">
+        <is>
+          <t>1.对称轴133张/陈致豪.JPG</t>
+        </is>
+      </c>
+      <c r="B124" t="n">
+        <v>0.021303</v>
+      </c>
+      <c r="C124" t="n">
+        <v>0.03294</v>
+      </c>
+      <c r="D124" t="n">
+        <v>0.035217</v>
+      </c>
+      <c r="E124" t="n">
+        <v>0.055867</v>
+      </c>
+      <c r="F124" t="n">
+        <v>0.008370000000000001</v>
+      </c>
+    </row>
+    <row r="125">
+      <c r="A125" t="inlineStr">
+        <is>
+          <t>1.对称轴133张/陈芷萱.JPG</t>
+        </is>
+      </c>
+      <c r="B125" t="n">
+        <v>0.030122</v>
+      </c>
+      <c r="C125" t="n">
+        <v>0.033155</v>
+      </c>
+      <c r="D125" t="n">
+        <v>0.014777</v>
+      </c>
+      <c r="E125" t="n">
+        <v>0.021041</v>
+      </c>
+      <c r="F125" t="n">
+        <v>0.022951</v>
+      </c>
+    </row>
+    <row r="126">
+      <c r="A126" t="inlineStr">
+        <is>
+          <t>1.对称轴133张/陈鑫慧.JPG</t>
+        </is>
+      </c>
+      <c r="B126" t="n">
+        <v>0.015221</v>
+      </c>
+      <c r="C126" t="n">
+        <v>0.016126</v>
+      </c>
+      <c r="D126" t="n">
+        <v>0.008029</v>
+      </c>
+      <c r="E126" t="n">
+        <v>0.011696</v>
+      </c>
+      <c r="F126" t="n">
+        <v>0.039723</v>
+      </c>
+    </row>
+    <row r="127">
+      <c r="A127" t="inlineStr">
+        <is>
+          <t>1.对称轴133张/陈雪梅.JPG</t>
+        </is>
+      </c>
+      <c r="B127" t="n">
+        <v>0.027427</v>
+      </c>
+      <c r="C127" t="n">
+        <v>0.011063</v>
+      </c>
+      <c r="D127" t="n">
+        <v>0.014447</v>
+      </c>
+      <c r="E127" t="n">
+        <v>0.023143</v>
+      </c>
+      <c r="F127" t="n">
+        <v>0.056862</v>
+      </c>
+    </row>
+    <row r="128">
+      <c r="A128" t="inlineStr">
+        <is>
+          <t>1.对称轴133张/陈露.JPG</t>
+        </is>
+      </c>
+      <c r="B128" t="n">
+        <v>0.01581</v>
+      </c>
+      <c r="C128" t="n">
+        <v>0.031761</v>
+      </c>
+      <c r="D128" t="n">
+        <v>0.015174</v>
+      </c>
+      <c r="E128" t="n">
+        <v>0.043036</v>
+      </c>
+      <c r="F128" t="n">
+        <v>0.052417</v>
+      </c>
+    </row>
+    <row r="129">
+      <c r="A129" t="inlineStr">
+        <is>
+          <t>1.对称轴133张/陈靓靓.JPG</t>
+        </is>
+      </c>
+      <c r="B129" t="n">
+        <v>0.039256</v>
+      </c>
+      <c r="C129" t="n">
+        <v>0.026532</v>
+      </c>
+      <c r="D129" t="n">
+        <v>0.021335</v>
+      </c>
+      <c r="E129" t="n">
+        <v>0.034706</v>
+      </c>
+      <c r="F129" t="n">
+        <v>0.06654</v>
+      </c>
+    </row>
+    <row r="130">
+      <c r="A130" t="inlineStr">
+        <is>
+          <t>1.对称轴133张/陈静怡.JPG</t>
+        </is>
+      </c>
+      <c r="B130" t="n">
+        <v>0.031627</v>
+      </c>
+      <c r="C130" t="n">
+        <v>0.029873</v>
+      </c>
+      <c r="D130" t="n">
+        <v>0.054861</v>
+      </c>
+      <c r="E130" t="n">
+        <v>0.05774</v>
+      </c>
+      <c r="F130" t="n">
+        <v>0.049128</v>
+      </c>
+    </row>
+    <row r="131">
+      <c r="A131" t="inlineStr">
+        <is>
+          <t>1.对称轴133张/陈韵旭.JPG</t>
+        </is>
+      </c>
+      <c r="B131" t="n">
+        <v>0.021502</v>
+      </c>
+      <c r="C131" t="n">
+        <v>0.009041</v>
+      </c>
+      <c r="D131" t="n">
+        <v>0.023397</v>
+      </c>
+      <c r="E131" t="n">
+        <v>0.031421</v>
+      </c>
+      <c r="F131" t="n">
+        <v>0.048088</v>
+      </c>
+    </row>
+    <row r="132">
+      <c r="A132" t="inlineStr">
+        <is>
+          <t>1.对称轴133张/陈麒文.JPG</t>
+        </is>
+      </c>
+      <c r="B132" t="n">
+        <v>0.04398</v>
+      </c>
+      <c r="C132" t="n">
+        <v>0.015939</v>
+      </c>
+      <c r="D132" t="n">
+        <v>0.001403</v>
+      </c>
+      <c r="E132" t="n">
+        <v>0.014195</v>
+      </c>
+      <c r="F132" t="n">
+        <v>0.080897</v>
+      </c>
+    </row>
+    <row r="133">
+      <c r="A133" t="inlineStr">
+        <is>
+          <t>2. 对称轴157张/付彩萍.JPG</t>
+        </is>
+      </c>
+      <c r="B133" t="n">
+        <v>0.022268</v>
+      </c>
+      <c r="C133" t="n">
+        <v>0.01987</v>
+      </c>
+      <c r="D133" t="n">
+        <v>0.022506</v>
+      </c>
+      <c r="E133" t="n">
+        <v>0.025213</v>
+      </c>
+      <c r="F133" t="n">
+        <v>0.037603</v>
+      </c>
+    </row>
+    <row r="134">
+      <c r="A134" t="inlineStr">
+        <is>
+          <t>2. 对称轴157张/伏丹.JPG</t>
+        </is>
+      </c>
+      <c r="B134" t="n">
+        <v>0.026787</v>
+      </c>
+      <c r="C134" t="n">
+        <v>0.016759</v>
+      </c>
+      <c r="D134" t="n">
+        <v>0.030999</v>
+      </c>
+      <c r="E134" t="n">
+        <v>0.050575</v>
+      </c>
+      <c r="F134" t="n">
+        <v>0.050013</v>
+      </c>
+    </row>
+    <row r="135">
+      <c r="A135" t="inlineStr">
+        <is>
+          <t>2. 对称轴157张/何亮.JPG</t>
+        </is>
+      </c>
+      <c r="B135" t="n">
+        <v>0.020699</v>
+      </c>
+      <c r="C135" t="n">
+        <v>0.026016</v>
+      </c>
+      <c r="D135" t="n">
+        <v>0.024553</v>
+      </c>
+      <c r="E135" t="n">
+        <v>0.024791</v>
+      </c>
+      <c r="F135" t="n">
+        <v>0.012311</v>
+      </c>
+    </row>
+    <row r="136">
+      <c r="A136" t="inlineStr">
+        <is>
+          <t>2. 对称轴157张/何俊梅.JPG</t>
+        </is>
+      </c>
+      <c r="B136" t="n">
+        <v>0.032736</v>
+      </c>
+      <c r="C136" t="n">
+        <v>0.015834</v>
+      </c>
+      <c r="D136" t="n">
+        <v>0.024479</v>
+      </c>
+      <c r="E136" t="n">
+        <v>0.018952</v>
+      </c>
+      <c r="F136" t="n">
+        <v>0.053421</v>
+      </c>
+    </row>
+    <row r="137">
+      <c r="A137" t="inlineStr">
+        <is>
+          <t>2. 对称轴157张/何婷.JPG</t>
+        </is>
+      </c>
+      <c r="B137" t="n">
+        <v>0.023039</v>
+      </c>
+      <c r="C137" t="n">
+        <v>0.023392</v>
+      </c>
+      <c r="D137" t="n">
+        <v>0.00756</v>
+      </c>
+      <c r="E137" t="n">
+        <v>0.009428000000000001</v>
+      </c>
+      <c r="F137" t="n">
+        <v>0.037105</v>
+      </c>
+    </row>
+    <row r="138">
+      <c r="A138" t="inlineStr">
+        <is>
+          <t>2. 对称轴157张/何宸郡.JPG</t>
+        </is>
+      </c>
+      <c r="B138" t="n">
+        <v>0.016664</v>
+      </c>
+      <c r="C138" t="n">
+        <v>0.017192</v>
+      </c>
+      <c r="D138" t="n">
+        <v>0.030658</v>
+      </c>
+      <c r="E138" t="n">
+        <v>0.013371</v>
+      </c>
+      <c r="F138" t="n">
+        <v>0.030372</v>
+      </c>
+    </row>
+    <row r="139">
+      <c r="A139" t="inlineStr">
+        <is>
+          <t>2. 对称轴157张/何晓清.JPG</t>
+        </is>
+      </c>
+      <c r="B139" t="n">
+        <v>0.01936</v>
+      </c>
+      <c r="C139" t="n">
+        <v>0.016041</v>
+      </c>
+      <c r="D139" t="n">
+        <v>0.005703</v>
+      </c>
+      <c r="E139" t="n">
+        <v>0.015689</v>
+      </c>
+      <c r="F139" t="n">
+        <v>0.03625</v>
+      </c>
+    </row>
+    <row r="140">
+      <c r="A140" t="inlineStr">
+        <is>
+          <t>2. 对称轴157张/何柠杉.JPG</t>
+        </is>
+      </c>
+      <c r="B140" t="n">
+        <v>0.016319</v>
+      </c>
+      <c r="C140" t="n">
+        <v>0.013767</v>
+      </c>
+      <c r="D140" t="n">
+        <v>0.032409</v>
+      </c>
+      <c r="E140" t="n">
+        <v>0.038222</v>
+      </c>
+      <c r="F140" t="n">
+        <v>0.07245699999999999</v>
+      </c>
+    </row>
+    <row r="141">
+      <c r="A141" t="inlineStr">
+        <is>
+          <t>2. 对称轴157张/何欢.JPG</t>
+        </is>
+      </c>
+      <c r="B141" t="n">
+        <v>0.041211</v>
+      </c>
+      <c r="C141" t="n">
+        <v>0.024658</v>
+      </c>
+      <c r="D141" t="n">
+        <v>0.016947</v>
+      </c>
+      <c r="E141" t="n">
+        <v>0.016095</v>
+      </c>
+      <c r="F141" t="n">
+        <v>0.065647</v>
+      </c>
+    </row>
+    <row r="142">
+      <c r="A142" t="inlineStr">
+        <is>
+          <t>2. 对称轴157张/何浩宇.JPG</t>
+        </is>
+      </c>
+      <c r="B142" t="n">
+        <v>0.020193</v>
+      </c>
+      <c r="C142" t="n">
+        <v>0.021744</v>
+      </c>
+      <c r="D142" t="n">
+        <v>0.020398</v>
+      </c>
+      <c r="E142" t="n">
+        <v>0.026745</v>
+      </c>
+      <c r="F142" t="n">
+        <v>0.041044</v>
+      </c>
+    </row>
+    <row r="143">
+      <c r="A143" t="inlineStr">
+        <is>
+          <t>2. 对称轴157张/何涵璐.JPG</t>
+        </is>
+      </c>
+      <c r="B143" t="n">
+        <v>0.025056</v>
+      </c>
+      <c r="C143" t="n">
+        <v>0.022606</v>
+      </c>
+      <c r="D143" t="n">
+        <v>0.013798</v>
+      </c>
+      <c r="E143" t="n">
+        <v>0.023068</v>
+      </c>
+      <c r="F143" t="n">
+        <v>0.039939</v>
+      </c>
+    </row>
+    <row r="144">
+      <c r="A144" t="inlineStr">
+        <is>
+          <t>2. 对称轴157张/何玙.JPG</t>
+        </is>
+      </c>
+      <c r="B144" t="n">
+        <v>0.026377</v>
+      </c>
+      <c r="C144" t="n">
+        <v>0.021892</v>
+      </c>
+      <c r="D144" t="n">
+        <v>0.023416</v>
+      </c>
+      <c r="E144" t="n">
+        <v>0.023242</v>
+      </c>
+      <c r="F144" t="n">
+        <v>0.026412</v>
+      </c>
+    </row>
+    <row r="145">
+      <c r="A145" t="inlineStr">
+        <is>
+          <t>2. 对称轴157张/何红春.JPG</t>
+        </is>
+      </c>
+      <c r="B145" t="n">
+        <v>0.015968</v>
+      </c>
+      <c r="C145" t="n">
+        <v>0.011016</v>
+      </c>
+      <c r="D145" t="n">
+        <v>0.01681</v>
+      </c>
+      <c r="E145" t="n">
+        <v>0.040605</v>
+      </c>
+      <c r="F145" t="n">
+        <v>0.032232</v>
+      </c>
+    </row>
+    <row r="146">
+      <c r="A146" t="inlineStr">
+        <is>
+          <t>2. 对称轴157张/何维.JPG</t>
+        </is>
+      </c>
+      <c r="B146" t="n">
+        <v>0.038801</v>
+      </c>
+      <c r="C146" t="n">
+        <v>0.011012</v>
+      </c>
+      <c r="D146" t="n">
+        <v>0.033485</v>
+      </c>
+      <c r="E146" t="n">
+        <v>0.056206</v>
+      </c>
+      <c r="F146" t="n">
+        <v>0.08665200000000001</v>
+      </c>
+    </row>
+    <row r="147">
+      <c r="A147" t="inlineStr">
+        <is>
+          <t>2. 对称轴157张/何美霖.JPG</t>
+        </is>
+      </c>
+      <c r="B147" t="n">
+        <v>0.046177</v>
+      </c>
+      <c r="C147" t="n">
+        <v>0.041789</v>
+      </c>
+      <c r="D147" t="n">
+        <v>0.0106</v>
+      </c>
+      <c r="E147" t="n">
+        <v>0.050483</v>
+      </c>
+      <c r="F147" t="n">
+        <v>0.07728500000000001</v>
+      </c>
+    </row>
+    <row r="148">
+      <c r="A148" t="inlineStr">
+        <is>
+          <t>2. 对称轴157张/何苗.JPG</t>
+        </is>
+      </c>
+      <c r="B148" t="n">
+        <v>0.031186</v>
+      </c>
+      <c r="C148" t="n">
+        <v>0.01407</v>
+      </c>
+      <c r="D148" t="n">
+        <v>0.010167</v>
+      </c>
+      <c r="E148" t="n">
+        <v>0.027384</v>
+      </c>
+      <c r="F148" t="n">
+        <v>0.063593</v>
+      </c>
+    </row>
+    <row r="149">
+      <c r="A149" t="inlineStr">
+        <is>
+          <t>2. 对称轴157张/何莲花.JPG</t>
+        </is>
+      </c>
+      <c r="B149" t="n">
+        <v>0.023361</v>
+      </c>
+      <c r="C149" t="n">
+        <v>0.019042</v>
+      </c>
+      <c r="D149" t="n">
+        <v>0.032342</v>
+      </c>
+      <c r="E149" t="n">
+        <v>0.038734</v>
+      </c>
+      <c r="F149" t="n">
+        <v>0.058518</v>
+      </c>
+    </row>
+    <row r="150">
+      <c r="A150" t="inlineStr">
+        <is>
+          <t>2. 对称轴157张/何蓉杰.JPG</t>
+        </is>
+      </c>
+      <c r="B150" t="n">
+        <v>0.03883</v>
+      </c>
+      <c r="C150" t="n">
+        <v>0.009827000000000001</v>
+      </c>
+      <c r="D150" t="n">
+        <v>0.006391</v>
+      </c>
+      <c r="E150" t="n">
+        <v>0.006026</v>
+      </c>
+      <c r="F150" t="n">
+        <v>0.04217</v>
+      </c>
+    </row>
+    <row r="151">
+      <c r="A151" t="inlineStr">
+        <is>
+          <t>2. 对称轴157张/何蕊西.JPG</t>
+        </is>
+      </c>
+      <c r="B151" t="n">
+        <v>0.041663</v>
+      </c>
+      <c r="C151" t="n">
+        <v>0.02012</v>
+      </c>
+      <c r="D151" t="n">
+        <v>0.029414</v>
+      </c>
+      <c r="E151" t="n">
+        <v>0.022562</v>
+      </c>
+      <c r="F151" t="n">
+        <v>0.015283</v>
+      </c>
+    </row>
+    <row r="152">
+      <c r="A152" t="inlineStr">
+        <is>
+          <t>2. 对称轴157张/何诺怡.JPG</t>
+        </is>
+      </c>
+      <c r="B152" t="n">
+        <v>0.023829</v>
+      </c>
+      <c r="C152" t="n">
+        <v>0.009178</v>
+      </c>
+      <c r="D152" t="n">
+        <v>0.008999999999999999</v>
+      </c>
+      <c r="E152" t="n">
+        <v>0.01116</v>
+      </c>
+      <c r="F152" t="n">
+        <v>0.042566</v>
+      </c>
+    </row>
+    <row r="153">
+      <c r="A153" t="inlineStr">
+        <is>
+          <t>2. 对称轴157张/何静.JPG</t>
+        </is>
+      </c>
+      <c r="B153" t="n">
+        <v>0.027992</v>
+      </c>
+      <c r="C153" t="n">
+        <v>0.018376</v>
+      </c>
+      <c r="D153" t="n">
+        <v>0.024048</v>
+      </c>
+      <c r="E153" t="n">
+        <v>0.021472</v>
+      </c>
+      <c r="F153" t="n">
+        <v>0.089867</v>
+      </c>
+    </row>
+    <row r="154">
+      <c r="A154" t="inlineStr">
+        <is>
+          <t>2. 对称轴157张/何静姝.JPG</t>
+        </is>
+      </c>
+      <c r="B154" t="n">
+        <v>0.020604</v>
+      </c>
+      <c r="C154" t="n">
+        <v>0.018118</v>
+      </c>
+      <c r="D154" t="n">
+        <v>0.009624000000000001</v>
+      </c>
+      <c r="E154" t="n">
+        <v>0.028233</v>
+      </c>
+      <c r="F154" t="n">
+        <v>0.050027</v>
+      </c>
+    </row>
+    <row r="155">
+      <c r="A155" t="inlineStr">
+        <is>
+          <t>2. 对称轴157张/侯博耀.JPG</t>
+        </is>
+      </c>
+      <c r="B155" t="n">
+        <v>0.024125</v>
+      </c>
+      <c r="C155" t="n">
+        <v>0.024542</v>
+      </c>
+      <c r="D155" t="n">
+        <v>0.010911</v>
+      </c>
+      <c r="E155" t="n">
+        <v>0.043255</v>
+      </c>
+      <c r="F155" t="n">
+        <v>0.07889599999999999</v>
+      </c>
+    </row>
+    <row r="156">
+      <c r="A156" t="inlineStr">
+        <is>
+          <t>2. 对称轴157张/侯蓉.JPG</t>
+        </is>
+      </c>
+      <c r="B156" t="n">
+        <v>0.031908</v>
+      </c>
+      <c r="C156" t="n">
+        <v>0.014259</v>
+      </c>
+      <c r="D156" t="n">
+        <v>0.026758</v>
+      </c>
+      <c r="E156" t="n">
+        <v>0.034742</v>
+      </c>
+      <c r="F156" t="n">
+        <v>0.044268</v>
+      </c>
+    </row>
+    <row r="157">
+      <c r="A157" t="inlineStr">
+        <is>
+          <t>2. 对称轴157张/兰于青.JPG</t>
+        </is>
+      </c>
+      <c r="B157" t="n">
+        <v>0.032936</v>
+      </c>
+      <c r="C157" t="n">
+        <v>0.021005</v>
+      </c>
+      <c r="D157" t="n">
+        <v>0.023518</v>
+      </c>
+      <c r="E157" t="n">
+        <v>0.043725</v>
+      </c>
+      <c r="F157" t="n">
+        <v>0.042208</v>
+      </c>
+    </row>
+    <row r="158">
+      <c r="A158" t="inlineStr">
+        <is>
+          <t>2. 对称轴157张/兰亦成.JPG</t>
+        </is>
+      </c>
+      <c r="B158" t="n">
+        <v>0.015418</v>
+      </c>
+      <c r="C158" t="n">
+        <v>0.013444</v>
+      </c>
+      <c r="D158" t="n">
+        <v>0.006307</v>
+      </c>
+      <c r="E158" t="n">
+        <v>0.010937</v>
+      </c>
+      <c r="F158" t="n">
+        <v>0.02305</v>
+      </c>
+    </row>
+    <row r="159">
+      <c r="A159" t="inlineStr">
+        <is>
+          <t>2. 对称轴157张/兰添.JPG</t>
+        </is>
+      </c>
+      <c r="B159" t="n">
+        <v>0.040662</v>
+      </c>
+      <c r="C159" t="n">
+        <v>0.035168</v>
+      </c>
+      <c r="D159" t="n">
+        <v>0.004436</v>
+      </c>
+      <c r="E159" t="n">
+        <v>0.052409</v>
+      </c>
+      <c r="F159" t="n">
+        <v>0.056186</v>
+      </c>
+    </row>
+    <row r="160">
+      <c r="A160" t="inlineStr">
+        <is>
+          <t>2. 对称轴157张/兰美慧.JPG</t>
+        </is>
+      </c>
+      <c r="B160" t="n">
+        <v>0.027436</v>
+      </c>
+      <c r="C160" t="n">
+        <v>0.016309</v>
+      </c>
+      <c r="D160" t="n">
+        <v>0.020099</v>
+      </c>
+      <c r="E160" t="n">
+        <v>0.02428</v>
+      </c>
+      <c r="F160" t="n">
+        <v>0.044094</v>
+      </c>
+    </row>
+    <row r="161">
+      <c r="A161" t="inlineStr">
+        <is>
+          <t>2. 对称轴157张/冯仁强.JPG</t>
+        </is>
+      </c>
+      <c r="B161" t="n">
+        <v>0.035628</v>
+      </c>
+      <c r="C161" t="n">
+        <v>0.029261</v>
+      </c>
+      <c r="D161" t="n">
+        <v>0.035629</v>
+      </c>
+      <c r="E161" t="n">
+        <v>0.042558</v>
+      </c>
+      <c r="F161" t="n">
+        <v>0.03831</v>
+      </c>
+    </row>
+    <row r="162">
+      <c r="A162" t="inlineStr">
+        <is>
+          <t>2. 对称轴157张/冯俐.JPG</t>
+        </is>
+      </c>
+      <c r="B162" t="n">
+        <v>0.019352</v>
+      </c>
+      <c r="C162" t="n">
+        <v>0.014765</v>
+      </c>
+      <c r="D162" t="n">
+        <v>0.005348</v>
+      </c>
+      <c r="E162" t="n">
+        <v>0.033393</v>
+      </c>
+      <c r="F162" t="n">
+        <v>0.050974</v>
+      </c>
+    </row>
+    <row r="163">
+      <c r="A163" t="inlineStr">
+        <is>
+          <t>2. 对称轴157张/冯圣兰.JPG</t>
+        </is>
+      </c>
+      <c r="B163" t="n">
+        <v>0.032932</v>
+      </c>
+      <c r="C163" t="n">
+        <v>0.026375</v>
+      </c>
+      <c r="D163" t="n">
+        <v>0.017978</v>
+      </c>
+      <c r="E163" t="n">
+        <v>0.027262</v>
+      </c>
+      <c r="F163" t="n">
+        <v>0.080085</v>
+      </c>
+    </row>
+    <row r="164">
+      <c r="A164" t="inlineStr">
+        <is>
+          <t>2. 对称轴157张/冯思瑶.JPG</t>
+        </is>
+      </c>
+      <c r="B164" t="n">
+        <v>0.014199</v>
+      </c>
+      <c r="C164" t="n">
+        <v>0.02287</v>
+      </c>
+      <c r="D164" t="n">
+        <v>0.009091999999999999</v>
+      </c>
+      <c r="E164" t="n">
+        <v>0.008795000000000001</v>
+      </c>
+      <c r="F164" t="n">
+        <v>0.037748</v>
+      </c>
+    </row>
+    <row r="165">
+      <c r="A165" t="inlineStr">
+        <is>
+          <t>2. 对称轴157张/冯梅.JPG</t>
+        </is>
+      </c>
+      <c r="B165" t="n">
+        <v>0.044228</v>
+      </c>
+      <c r="C165" t="n">
+        <v>0.01716</v>
+      </c>
+      <c r="D165" t="n">
+        <v>0.034122</v>
+      </c>
+      <c r="E165" t="n">
+        <v>0.017966</v>
+      </c>
+      <c r="F165" t="n">
+        <v>0.04627</v>
+      </c>
+    </row>
+    <row r="166">
+      <c r="A166" t="inlineStr">
+        <is>
+          <t>2. 对称轴157张/冯浩林.JPG</t>
+        </is>
+      </c>
+      <c r="B166" t="n">
+        <v>0.022028</v>
+      </c>
+      <c r="C166" t="n">
+        <v>0.014494</v>
+      </c>
+      <c r="D166" t="n">
+        <v>0.011413</v>
+      </c>
+      <c r="E166" t="n">
+        <v>0.019143</v>
+      </c>
+      <c r="F166" t="n">
+        <v>0.035213</v>
+      </c>
+    </row>
+    <row r="167">
+      <c r="A167" t="inlineStr">
+        <is>
+          <t>2. 对称轴157张/冯禹睿.JPG</t>
+        </is>
+      </c>
+      <c r="B167" t="n">
+        <v>0.031323</v>
+      </c>
+      <c r="C167" t="n">
+        <v>0.016819</v>
+      </c>
+      <c r="D167" t="n">
+        <v>0.025849</v>
+      </c>
+      <c r="E167" t="n">
+        <v>0.011915</v>
+      </c>
+      <c r="F167" t="n">
+        <v>0.035253</v>
+      </c>
+    </row>
+    <row r="168">
+      <c r="A168" t="inlineStr">
+        <is>
+          <t>2. 对称轴157张/冯耀杰.JPG</t>
+        </is>
+      </c>
+      <c r="B168" t="n">
+        <v>0.029835</v>
+      </c>
+      <c r="C168" t="n">
+        <v>0.022079</v>
+      </c>
+      <c r="D168" t="n">
+        <v>0.033062</v>
+      </c>
+      <c r="E168" t="n">
+        <v>0.052863</v>
+      </c>
+      <c r="F168" t="n">
+        <v>0.10223</v>
+      </c>
+    </row>
+    <row r="169">
+      <c r="A169" t="inlineStr">
+        <is>
+          <t>2. 对称轴157张/古良玉.JPG</t>
+        </is>
+      </c>
+      <c r="B169" t="n">
+        <v>0.036948</v>
+      </c>
+      <c r="C169" t="n">
+        <v>0.021782</v>
+      </c>
+      <c r="D169" t="n">
+        <v>0.039579</v>
+      </c>
+      <c r="E169" t="n">
+        <v>0.037439</v>
+      </c>
+      <c r="F169" t="n">
+        <v>0.099013</v>
+      </c>
+    </row>
+    <row r="170">
+      <c r="A170" t="inlineStr">
+        <is>
+          <t>2. 对称轴157张/吉如意.JPG</t>
+        </is>
+      </c>
+      <c r="B170" t="n">
+        <v>0.027054</v>
+      </c>
+      <c r="C170" t="n">
+        <v>0.016147</v>
+      </c>
+      <c r="D170" t="n">
+        <v>0.021735</v>
+      </c>
+      <c r="E170" t="n">
+        <v>0.040498</v>
+      </c>
+      <c r="F170" t="n">
+        <v>0.077408</v>
+      </c>
+    </row>
+    <row r="171">
+      <c r="A171" t="inlineStr">
+        <is>
+          <t>2. 对称轴157张/吉方圆.JPG</t>
+        </is>
+      </c>
+      <c r="B171" t="n">
+        <v>0.023118</v>
+      </c>
+      <c r="C171" t="n">
+        <v>0.010721</v>
+      </c>
+      <c r="D171" t="n">
+        <v>0.015901</v>
+      </c>
+      <c r="E171" t="n">
+        <v>0.03311</v>
+      </c>
+      <c r="F171" t="n">
+        <v>0.077873</v>
+      </c>
+    </row>
+    <row r="172">
+      <c r="A172" t="inlineStr">
+        <is>
+          <t>2. 对称轴157张/姜添.JPG</t>
+        </is>
+      </c>
+      <c r="B172" t="n">
+        <v>0.045446</v>
+      </c>
+      <c r="C172" t="n">
+        <v>0.014696</v>
+      </c>
+      <c r="D172" t="n">
+        <v>0.011221</v>
+      </c>
+      <c r="E172" t="n">
+        <v>0.018373</v>
+      </c>
+      <c r="F172" t="n">
+        <v>0.06486</v>
+      </c>
+    </row>
+    <row r="173">
+      <c r="A173" t="inlineStr">
+        <is>
+          <t>2. 对称轴157张/孔晨轩.JPG</t>
+        </is>
+      </c>
+      <c r="B173" t="n">
+        <v>0.019176</v>
+      </c>
+      <c r="C173" t="n">
+        <v>0.012294</v>
+      </c>
+      <c r="D173" t="n">
+        <v>0.010688</v>
+      </c>
+      <c r="E173" t="n">
+        <v>0.016005</v>
+      </c>
+      <c r="F173" t="n">
+        <v>0.02394</v>
+      </c>
+    </row>
+    <row r="174">
+      <c r="A174" t="inlineStr">
+        <is>
+          <t>2. 对称轴157张/官昊融.JPG</t>
+        </is>
+      </c>
+      <c r="B174" t="n">
+        <v>0.031152</v>
+      </c>
+      <c r="C174" t="n">
+        <v>0.010629</v>
+      </c>
+      <c r="D174" t="n">
+        <v>0.033766</v>
+      </c>
+      <c r="E174" t="n">
+        <v>0.04062</v>
+      </c>
+      <c r="F174" t="n">
+        <v>0.059064</v>
+      </c>
+    </row>
+    <row r="175">
+      <c r="A175" t="inlineStr">
+        <is>
+          <t>2. 对称轴157张/官露婷.JPG</t>
+        </is>
+      </c>
+      <c r="B175" t="n">
+        <v>0.018977</v>
+      </c>
+      <c r="C175" t="n">
+        <v>0.00695</v>
+      </c>
+      <c r="D175" t="n">
+        <v>0.012806</v>
+      </c>
+      <c r="E175" t="n">
+        <v>0.018153</v>
+      </c>
+      <c r="F175" t="n">
+        <v>0.01709</v>
+      </c>
+    </row>
+    <row r="176">
+      <c r="A176" t="inlineStr">
+        <is>
+          <t>2. 对称轴157张/巨熙.JPG</t>
+        </is>
+      </c>
+      <c r="B176" t="n">
+        <v>0.01655</v>
+      </c>
+      <c r="C176" t="n">
+        <v>0.015828</v>
+      </c>
+      <c r="D176" t="n">
+        <v>0.022777</v>
+      </c>
+      <c r="E176" t="n">
+        <v>0.016211</v>
+      </c>
+      <c r="F176" t="n">
+        <v>0.050267</v>
+      </c>
+    </row>
+    <row r="177">
+      <c r="A177" t="inlineStr">
+        <is>
+          <t>2. 对称轴157张/康钟佩.JPG</t>
+        </is>
+      </c>
+      <c r="B177" t="n">
+        <v>0.03885</v>
+      </c>
+      <c r="C177" t="n">
+        <v>0.020132</v>
+      </c>
+      <c r="D177" t="n">
+        <v>0.015854</v>
+      </c>
+      <c r="E177" t="n">
+        <v>0.030815</v>
+      </c>
+      <c r="F177" t="n">
+        <v>0.02629</v>
+      </c>
+    </row>
+    <row r="178">
+      <c r="A178" t="inlineStr">
+        <is>
+          <t>2. 对称轴157张/敬俊.JPG</t>
+        </is>
+      </c>
+      <c r="B178" t="n">
+        <v>0.043254</v>
+      </c>
+      <c r="C178" t="n">
+        <v>0.025025</v>
+      </c>
+      <c r="D178" t="n">
+        <v>0.024257</v>
+      </c>
+      <c r="E178" t="n">
+        <v>0.020506</v>
+      </c>
+      <c r="F178" t="n">
+        <v>0.068748</v>
+      </c>
+    </row>
+    <row r="179">
+      <c r="A179" t="inlineStr">
+        <is>
+          <t>2. 对称轴157张/敬小耘.JPG</t>
+        </is>
+      </c>
+      <c r="B179" t="n">
+        <v>0.015617</v>
+      </c>
+      <c r="C179" t="n">
+        <v>0.020637</v>
+      </c>
+      <c r="D179" t="n">
+        <v>0.00269</v>
+      </c>
+      <c r="E179" t="n">
+        <v>0.016971</v>
+      </c>
+      <c r="F179" t="n">
+        <v>0.03186</v>
+      </c>
+    </row>
+    <row r="180">
+      <c r="A180" t="inlineStr">
+        <is>
+          <t>2. 对称轴157张/景光州.JPG</t>
+        </is>
+      </c>
+      <c r="B180" t="n">
+        <v>0.019137</v>
+      </c>
+      <c r="C180" t="n">
+        <v>0.015785</v>
+      </c>
+      <c r="D180" t="n">
+        <v>0.03686</v>
+      </c>
+      <c r="E180" t="n">
+        <v>0.056513</v>
+      </c>
+      <c r="F180" t="n">
+        <v>0.087199</v>
+      </c>
+    </row>
+    <row r="181">
+      <c r="A181" t="inlineStr">
+        <is>
+          <t>2. 对称轴157张/李丽偲.JPG</t>
+        </is>
+      </c>
+      <c r="B181" t="n">
+        <v>0.026401</v>
+      </c>
+      <c r="C181" t="n">
+        <v>0.031294</v>
+      </c>
+      <c r="D181" t="n">
+        <v>0.0068</v>
+      </c>
+      <c r="E181" t="n">
+        <v>0.022389</v>
+      </c>
+      <c r="F181" t="n">
+        <v>0.00898</v>
+      </c>
+    </row>
+    <row r="182">
+      <c r="A182" t="inlineStr">
+        <is>
+          <t>2. 对称轴157张/李伯忱.JPG</t>
+        </is>
+      </c>
+      <c r="B182" t="n">
+        <v>0.035223</v>
+      </c>
+      <c r="C182" t="n">
+        <v>0.025327</v>
+      </c>
+      <c r="D182" t="n">
+        <v>0.000328</v>
+      </c>
+      <c r="E182" t="n">
+        <v>0.035119</v>
+      </c>
+      <c r="F182" t="n">
+        <v>0.026471</v>
+      </c>
+    </row>
+    <row r="183">
+      <c r="A183" t="inlineStr">
+        <is>
+          <t>2. 对称轴157张/李佳.JPG</t>
+        </is>
+      </c>
+      <c r="B183" t="n">
+        <v>0.015236</v>
+      </c>
+      <c r="C183" t="n">
+        <v>0.014614</v>
+      </c>
+      <c r="D183" t="n">
+        <v>0.011588</v>
+      </c>
+      <c r="E183" t="n">
+        <v>0.007885</v>
+      </c>
+      <c r="F183" t="n">
+        <v>0.008437999999999999</v>
+      </c>
+    </row>
+    <row r="184">
+      <c r="A184" t="inlineStr">
+        <is>
+          <t>2. 对称轴157张/李佳镁.JPG</t>
+        </is>
+      </c>
+      <c r="B184" t="n">
+        <v>0.037228</v>
+      </c>
+      <c r="C184" t="n">
+        <v>0.031734</v>
+      </c>
+      <c r="D184" t="n">
+        <v>0.016737</v>
+      </c>
+      <c r="E184" t="n">
+        <v>0.034458</v>
+      </c>
+      <c r="F184" t="n">
+        <v>0.041973</v>
+      </c>
+    </row>
+    <row r="185">
+      <c r="A185" t="inlineStr">
+        <is>
+          <t>2. 对称轴157张/李俊豪.JPG</t>
+        </is>
+      </c>
+      <c r="B185" t="n">
+        <v>0.036966</v>
+      </c>
+      <c r="C185" t="n">
+        <v>0.023887</v>
+      </c>
+      <c r="D185" t="n">
+        <v>0.031127</v>
+      </c>
+      <c r="E185" t="n">
+        <v>0.035923</v>
+      </c>
+      <c r="F185" t="n">
+        <v>0.105207</v>
+      </c>
+    </row>
+    <row r="186">
+      <c r="A186" t="inlineStr">
+        <is>
+          <t>2. 对称轴157张/李冬欣.JPG</t>
+        </is>
+      </c>
+      <c r="B186" t="n">
+        <v>0.030349</v>
+      </c>
+      <c r="C186" t="n">
+        <v>0.025255</v>
+      </c>
+      <c r="D186" t="n">
+        <v>0.017802</v>
+      </c>
+      <c r="E186" t="n">
+        <v>0.047334</v>
+      </c>
+      <c r="F186" t="n">
+        <v>0.073004</v>
+      </c>
+    </row>
+    <row r="187">
+      <c r="A187" t="inlineStr">
+        <is>
+          <t>2. 对称轴157张/李博.JPG</t>
+        </is>
+      </c>
+      <c r="B187" t="n">
+        <v>0.037197</v>
+      </c>
+      <c r="C187" t="n">
+        <v>0.017529</v>
+      </c>
+      <c r="D187" t="n">
+        <v>0.006595</v>
+      </c>
+      <c r="E187" t="n">
+        <v>0.032567</v>
+      </c>
+      <c r="F187" t="n">
+        <v>0.014766</v>
+      </c>
+    </row>
+    <row r="188">
+      <c r="A188" t="inlineStr">
+        <is>
+          <t>2. 对称轴157张/李嘉惠.JPG</t>
+        </is>
+      </c>
+      <c r="B188" t="n">
+        <v>0.019317</v>
+      </c>
+      <c r="C188" t="n">
+        <v>0.010547</v>
+      </c>
+      <c r="D188" t="n">
+        <v>0.055958</v>
+      </c>
+      <c r="E188" t="n">
+        <v>0.033122</v>
+      </c>
+      <c r="F188" t="n">
+        <v>0.066348</v>
+      </c>
+    </row>
+    <row r="189">
+      <c r="A189" t="inlineStr">
+        <is>
+          <t>2. 对称轴157张/李孟阳.JPG</t>
+        </is>
+      </c>
+      <c r="B189" t="n">
+        <v>0.027343</v>
+      </c>
+      <c r="C189" t="n">
+        <v>0.017441</v>
+      </c>
+      <c r="D189" t="n">
+        <v>0.003719</v>
+      </c>
+      <c r="E189" t="n">
+        <v>0.026967</v>
+      </c>
+      <c r="F189" t="n">
+        <v>0.050888</v>
+      </c>
+    </row>
+    <row r="190">
+      <c r="A190" t="inlineStr">
+        <is>
+          <t>2. 对称轴157张/李昌朔.JPG</t>
+        </is>
+      </c>
+      <c r="B190" t="n">
+        <v>0.028049</v>
+      </c>
+      <c r="C190" t="n">
+        <v>0.008852</v>
+      </c>
+      <c r="D190" t="n">
+        <v>0.007541</v>
+      </c>
+      <c r="E190" t="n">
+        <v>0.029792</v>
+      </c>
+      <c r="F190" t="n">
+        <v>0.054487</v>
+      </c>
+    </row>
+    <row r="191">
+      <c r="A191" t="inlineStr">
+        <is>
+          <t>2. 对称轴157张/李晨语.JPG</t>
+        </is>
+      </c>
+      <c r="B191" t="n">
+        <v>0.032995</v>
+      </c>
+      <c r="C191" t="n">
+        <v>0.012111</v>
+      </c>
+      <c r="D191" t="n">
+        <v>0.02301</v>
+      </c>
+      <c r="E191" t="n">
+        <v>0.010044</v>
+      </c>
+      <c r="F191" t="n">
+        <v>0.023848</v>
+      </c>
+    </row>
+    <row r="192">
+      <c r="A192" t="inlineStr">
+        <is>
+          <t>2. 对称轴157张/李林蔚.JPG</t>
+        </is>
+      </c>
+      <c r="B192" t="n">
+        <v>0.029037</v>
+      </c>
+      <c r="C192" t="n">
+        <v>0.019342</v>
+      </c>
+      <c r="D192" t="n">
+        <v>0.00734</v>
+      </c>
+      <c r="E192" t="n">
+        <v>0.011524</v>
+      </c>
+      <c r="F192" t="n">
+        <v>0.051785</v>
+      </c>
+    </row>
+    <row r="193">
+      <c r="A193" t="inlineStr">
+        <is>
+          <t>2. 对称轴157张/李果.JPG</t>
+        </is>
+      </c>
+      <c r="B193" t="n">
+        <v>0.045418</v>
+      </c>
+      <c r="C193" t="n">
+        <v>0.043725</v>
+      </c>
+      <c r="D193" t="n">
+        <v>0.019203</v>
+      </c>
+      <c r="E193" t="n">
+        <v>0.039088</v>
+      </c>
+      <c r="F193" t="n">
+        <v>0.047409</v>
+      </c>
+    </row>
+    <row r="194">
+      <c r="A194" t="inlineStr">
+        <is>
+          <t>2. 对称轴157张/李柯兴.JPG</t>
+        </is>
+      </c>
+      <c r="B194" t="n">
+        <v>0.021201</v>
+      </c>
+      <c r="C194" t="n">
+        <v>0.020892</v>
+      </c>
+      <c r="D194" t="n">
+        <v>0.023899</v>
+      </c>
+      <c r="E194" t="n">
+        <v>0.010408</v>
+      </c>
+      <c r="F194" t="n">
+        <v>0.016657</v>
+      </c>
+    </row>
+    <row r="195">
+      <c r="A195" t="inlineStr">
+        <is>
+          <t>2. 对称轴157张/李柳梅.JPG</t>
+        </is>
+      </c>
+      <c r="B195" t="n">
+        <v>0.012974</v>
+      </c>
+      <c r="C195" t="n">
+        <v>0.012351</v>
+      </c>
+      <c r="D195" t="n">
+        <v>0.017402</v>
+      </c>
+      <c r="E195" t="n">
+        <v>0.015086</v>
+      </c>
+      <c r="F195" t="n">
+        <v>0.024905</v>
+      </c>
+    </row>
+    <row r="196">
+      <c r="A196" t="inlineStr">
+        <is>
+          <t>2. 对称轴157张/李梅.JPG</t>
+        </is>
+      </c>
+      <c r="B196" t="n">
+        <v>0.01984</v>
+      </c>
+      <c r="C196" t="n">
+        <v>0.028345</v>
+      </c>
+      <c r="D196" t="n">
+        <v>0.031672</v>
+      </c>
+      <c r="E196" t="n">
+        <v>0.02913</v>
+      </c>
+      <c r="F196" t="n">
+        <v>0.024676</v>
+      </c>
+    </row>
+    <row r="197">
+      <c r="A197" t="inlineStr">
+        <is>
+          <t>2. 对称轴157张/李海升.JPG</t>
+        </is>
+      </c>
+      <c r="B197" t="n">
+        <v>0.038316</v>
+      </c>
+      <c r="C197" t="n">
+        <v>0.023644</v>
+      </c>
+      <c r="D197" t="n">
+        <v>0.005482</v>
+      </c>
+      <c r="E197" t="n">
+        <v>0.01198</v>
+      </c>
+      <c r="F197" t="n">
+        <v>0.043216</v>
+      </c>
+    </row>
+    <row r="198">
+      <c r="A198" t="inlineStr">
+        <is>
+          <t>2. 对称轴157张/李海树.JPG</t>
+        </is>
+      </c>
+      <c r="B198" t="n">
+        <v>0.030991</v>
+      </c>
+      <c r="C198" t="n">
+        <v>0.029963</v>
+      </c>
+      <c r="D198" t="n">
+        <v>0.014346</v>
+      </c>
+      <c r="E198" t="n">
+        <v>0.024529</v>
+      </c>
+      <c r="F198" t="n">
+        <v>0.014364</v>
+      </c>
+    </row>
+    <row r="199">
+      <c r="A199" t="inlineStr">
+        <is>
+          <t>2. 对称轴157张/李璐杉.JPG</t>
+        </is>
+      </c>
+      <c r="B199" t="n">
+        <v>0.012236</v>
+      </c>
+      <c r="C199" t="n">
+        <v>0.016331</v>
+      </c>
+      <c r="D199" t="n">
+        <v>0.008718</v>
+      </c>
+      <c r="E199" t="n">
+        <v>0.024347</v>
+      </c>
+      <c r="F199" t="n">
+        <v>0.023178</v>
+      </c>
+    </row>
+    <row r="200">
+      <c r="A200" t="inlineStr">
+        <is>
+          <t>2. 对称轴157张/李翠莲.JPG</t>
+        </is>
+      </c>
+      <c r="B200" t="n">
+        <v>0.017356</v>
+      </c>
+      <c r="C200" t="n">
+        <v>0.013172</v>
+      </c>
+      <c r="D200" t="n">
+        <v>0.028812</v>
+      </c>
+      <c r="E200" t="n">
+        <v>0.014785</v>
+      </c>
+      <c r="F200" t="n">
+        <v>0.014142</v>
+      </c>
+    </row>
+    <row r="201">
+      <c r="A201" t="inlineStr">
+        <is>
+          <t>2. 对称轴157张/李艾凌.JPG</t>
+        </is>
+      </c>
+      <c r="B201" t="n">
+        <v>0.029693</v>
+      </c>
+      <c r="C201" t="n">
+        <v>0.017981</v>
+      </c>
+      <c r="D201" t="n">
+        <v>0.010865</v>
+      </c>
+      <c r="E201" t="n">
+        <v>0.007606</v>
+      </c>
+      <c r="F201" t="n">
+        <v>0.042022</v>
+      </c>
+    </row>
+    <row r="202">
+      <c r="A202" t="inlineStr">
+        <is>
+          <t>2. 对称轴157张/李艾恬.JPG</t>
+        </is>
+      </c>
+      <c r="B202" t="n">
+        <v>0.017232</v>
+      </c>
+      <c r="C202" t="n">
+        <v>0.019205</v>
+      </c>
+      <c r="D202" t="n">
+        <v>0.038324</v>
+      </c>
+      <c r="E202" t="n">
+        <v>0.0468</v>
+      </c>
+      <c r="F202" t="n">
+        <v>0.106976</v>
+      </c>
+    </row>
+    <row r="203">
+      <c r="A203" t="inlineStr">
+        <is>
+          <t>2. 对称轴157张/李莉.JPG</t>
+        </is>
+      </c>
+      <c r="B203" t="n">
+        <v>0.017242</v>
+      </c>
+      <c r="C203" t="n">
+        <v>0.017299</v>
+      </c>
+      <c r="D203" t="n">
+        <v>0.023244</v>
+      </c>
+      <c r="E203" t="n">
+        <v>0.029341</v>
+      </c>
+      <c r="F203" t="n">
+        <v>0.050798</v>
+      </c>
+    </row>
+    <row r="204">
+      <c r="A204" t="inlineStr">
+        <is>
+          <t>2. 对称轴157张/李蔓青.JPG</t>
+        </is>
+      </c>
+      <c r="B204" t="n">
+        <v>0.01729</v>
+      </c>
+      <c r="C204" t="n">
+        <v>0.017908</v>
+      </c>
+      <c r="D204" t="n">
+        <v>0.01804</v>
+      </c>
+      <c r="E204" t="n">
+        <v>0.029302</v>
+      </c>
+      <c r="F204" t="n">
+        <v>0.037277</v>
+      </c>
+    </row>
+    <row r="205">
+      <c r="A205" t="inlineStr">
+        <is>
+          <t>2. 对称轴157张/李蕾.JPG</t>
+        </is>
+      </c>
+      <c r="B205" t="n">
+        <v>0.013161</v>
+      </c>
+      <c r="C205" t="n">
+        <v>0.015625</v>
+      </c>
+      <c r="D205" t="n">
+        <v>0.01392</v>
+      </c>
+      <c r="E205" t="n">
+        <v>0.01496</v>
+      </c>
+      <c r="F205" t="n">
+        <v>0.054447</v>
+      </c>
+    </row>
+    <row r="206">
+      <c r="A206" t="inlineStr">
+        <is>
+          <t>2. 对称轴157张/李金春.JPG</t>
+        </is>
+      </c>
+      <c r="B206" t="n">
+        <v>0.029977</v>
+      </c>
+      <c r="C206" t="n">
+        <v>0.020404</v>
+      </c>
+      <c r="D206" t="n">
+        <v>0.014717</v>
+      </c>
+      <c r="E206" t="n">
+        <v>0.030479</v>
+      </c>
+      <c r="F206" t="n">
+        <v>0.083505</v>
+      </c>
+    </row>
+    <row r="207">
+      <c r="A207" t="inlineStr">
+        <is>
+          <t>2. 对称轴157张/李金铭.JPG</t>
+        </is>
+      </c>
+      <c r="B207" t="n">
+        <v>0.032902</v>
+      </c>
+      <c r="C207" t="n">
+        <v>0.018722</v>
+      </c>
+      <c r="D207" t="n">
+        <v>0.029207</v>
+      </c>
+      <c r="E207" t="n">
+        <v>0.036332</v>
+      </c>
+      <c r="F207" t="n">
+        <v>0.060668</v>
+      </c>
+    </row>
+    <row r="208">
+      <c r="A208" t="inlineStr">
+        <is>
+          <t>2. 对称轴157张/李锦烨.JPG</t>
+        </is>
+      </c>
+      <c r="B208" t="n">
+        <v>0.036982</v>
+      </c>
+      <c r="C208" t="n">
+        <v>0.011779</v>
+      </c>
+      <c r="D208" t="n">
+        <v>0.006454</v>
+      </c>
+      <c r="E208" t="n">
+        <v>0.025955</v>
+      </c>
+      <c r="F208" t="n">
+        <v>0.084731</v>
+      </c>
+    </row>
+    <row r="209">
+      <c r="A209" t="inlineStr">
+        <is>
+          <t>2. 对称轴157张/柯倩.JPG</t>
+        </is>
+      </c>
+      <c r="B209" t="n">
+        <v>0.038854</v>
+      </c>
+      <c r="C209" t="n">
+        <v>0.014228</v>
+      </c>
+      <c r="D209" t="n">
+        <v>0.016943</v>
+      </c>
+      <c r="E209" t="n">
+        <v>0.011725</v>
+      </c>
+      <c r="F209" t="n">
+        <v>0.07944</v>
+      </c>
+    </row>
+    <row r="210">
+      <c r="A210" t="inlineStr">
+        <is>
+          <t>2. 对称轴157张/江旭刚.JPG</t>
+        </is>
+      </c>
+      <c r="B210" t="n">
+        <v>0.042614</v>
+      </c>
+      <c r="C210" t="n">
+        <v>0.015339</v>
+      </c>
+      <c r="D210" t="n">
+        <v>0.013012</v>
+      </c>
+      <c r="E210" t="n">
+        <v>0.025668</v>
+      </c>
+      <c r="F210" t="n">
+        <v>0.030895</v>
+      </c>
+    </row>
+    <row r="211">
+      <c r="A211" t="inlineStr">
+        <is>
+          <t>2. 对称轴157张/江明月.JPG</t>
+        </is>
+      </c>
+      <c r="B211" t="n">
+        <v>0.035229</v>
+      </c>
+      <c r="C211" t="n">
+        <v>0.007167</v>
+      </c>
+      <c r="D211" t="n">
+        <v>0.039461</v>
+      </c>
+      <c r="E211" t="n">
+        <v>0.025667</v>
+      </c>
+      <c r="F211" t="n">
+        <v>0.041267</v>
+      </c>
+    </row>
+    <row r="212">
+      <c r="A212" t="inlineStr">
+        <is>
+          <t>2. 对称轴157张/江浩宇.JPG</t>
+        </is>
+      </c>
+      <c r="B212" t="n">
+        <v>0.028977</v>
+      </c>
+      <c r="C212" t="n">
+        <v>0.008898</v>
+      </c>
+      <c r="D212" t="n">
+        <v>0.007677</v>
+      </c>
+      <c r="E212" t="n">
+        <v>0.032594</v>
+      </c>
+      <c r="F212" t="n">
+        <v>0.031615</v>
+      </c>
+    </row>
+    <row r="213">
+      <c r="A213" t="inlineStr">
+        <is>
+          <t>2. 对称轴157张/江知晓.JPG</t>
+        </is>
+      </c>
+      <c r="B213" t="n">
+        <v>0.033458</v>
+      </c>
+      <c r="C213" t="n">
+        <v>0.016453</v>
+      </c>
+      <c r="D213" t="n">
+        <v>0.018908</v>
+      </c>
+      <c r="E213" t="n">
+        <v>0.026103</v>
+      </c>
+      <c r="F213" t="n">
+        <v>0.025053</v>
+      </c>
+    </row>
+    <row r="214">
+      <c r="A214" t="inlineStr">
+        <is>
+          <t>2. 对称轴157张/江竞航.JPG</t>
+        </is>
+      </c>
+      <c r="B214" t="n">
+        <v>0.024913</v>
+      </c>
+      <c r="C214" t="n">
+        <v>0.016853</v>
+      </c>
+      <c r="D214" t="n">
+        <v>0.008486</v>
+      </c>
+      <c r="E214" t="n">
+        <v>0.01979</v>
+      </c>
+      <c r="F214" t="n">
+        <v>0.026241</v>
+      </c>
+    </row>
+    <row r="215">
+      <c r="A215" t="inlineStr">
+        <is>
+          <t>2. 对称轴157张/江鑫锐.JPG</t>
+        </is>
+      </c>
+      <c r="B215" t="n">
+        <v>0.018606</v>
+      </c>
+      <c r="C215" t="n">
+        <v>0.021758</v>
+      </c>
+      <c r="D215" t="n">
+        <v>0.013485</v>
+      </c>
+      <c r="E215" t="n">
+        <v>0.046728</v>
+      </c>
+      <c r="F215" t="n">
+        <v>0.07385899999999999</v>
+      </c>
+    </row>
+    <row r="216">
+      <c r="A216" t="inlineStr">
+        <is>
+          <t>2. 对称轴157张/管梓岑.JPG</t>
+        </is>
+      </c>
+      <c r="B216" t="n">
+        <v>0.018794</v>
+      </c>
+      <c r="C216" t="n">
+        <v>0.012309</v>
+      </c>
+      <c r="D216" t="n">
+        <v>0.009866</v>
+      </c>
+      <c r="E216" t="n">
+        <v>0.030528</v>
+      </c>
+      <c r="F216" t="n">
+        <v>0.061161</v>
+      </c>
+    </row>
+    <row r="217">
+      <c r="A217" t="inlineStr">
+        <is>
+          <t>2. 对称轴157张/胡峻铭.JPG</t>
+        </is>
+      </c>
+      <c r="B217" t="n">
+        <v>0.025836</v>
+      </c>
+      <c r="C217" t="n">
+        <v>0.018803</v>
+      </c>
+      <c r="D217" t="n">
+        <v>0.021561</v>
+      </c>
+      <c r="E217" t="n">
+        <v>0.023272</v>
+      </c>
+      <c r="F217" t="n">
+        <v>0.013322</v>
+      </c>
+    </row>
+    <row r="218">
+      <c r="A218" t="inlineStr">
+        <is>
+          <t>2. 对称轴157张/胡晓.JPG</t>
+        </is>
+      </c>
+      <c r="B218" t="n">
+        <v>0.010064</v>
+      </c>
+      <c r="C218" t="n">
+        <v>0.008767</v>
+      </c>
+      <c r="D218" t="n">
+        <v>0.018109</v>
+      </c>
+      <c r="E218" t="n">
+        <v>0.025023</v>
+      </c>
+      <c r="F218" t="n">
+        <v>0.054605</v>
+      </c>
+    </row>
+    <row r="219">
+      <c r="A219" t="inlineStr">
+        <is>
+          <t>2. 对称轴157张/胡晓毅.JPG</t>
+        </is>
+      </c>
+      <c r="B219" t="n">
+        <v>0.028358</v>
+      </c>
+      <c r="C219" t="n">
+        <v>0.034603</v>
+      </c>
+      <c r="D219" t="n">
+        <v>0.018332</v>
+      </c>
+      <c r="E219" t="n">
+        <v>0.06198</v>
+      </c>
+      <c r="F219" t="n">
+        <v>0.054901</v>
+      </c>
+    </row>
+    <row r="220">
+      <c r="A220" t="inlineStr">
+        <is>
+          <t>2. 对称轴157张/胡晖楠.JPG</t>
+        </is>
+      </c>
+      <c r="B220" t="n">
+        <v>0.012111</v>
+      </c>
+      <c r="C220" t="n">
+        <v>0.017307</v>
+      </c>
+      <c r="D220" t="n">
+        <v>0.035639</v>
+      </c>
+      <c r="E220" t="n">
+        <v>0.023505</v>
+      </c>
+      <c r="F220" t="n">
+        <v>0.068261</v>
+      </c>
+    </row>
+    <row r="221">
+      <c r="A221" t="inlineStr">
+        <is>
+          <t>2. 对称轴157张/胡浩洋.JPG</t>
+        </is>
+      </c>
+      <c r="B221" t="n">
+        <v>0.020744</v>
+      </c>
+      <c r="C221" t="n">
+        <v>0.011197</v>
+      </c>
+      <c r="D221" t="n">
+        <v>0.027379</v>
+      </c>
+      <c r="E221" t="n">
+        <v>0.0256</v>
+      </c>
+      <c r="F221" t="n">
+        <v>0.06535100000000001</v>
+      </c>
+    </row>
+    <row r="222">
+      <c r="A222" t="inlineStr">
+        <is>
+          <t>2. 对称轴157张/胡芷毓.JPG</t>
+        </is>
+      </c>
+      <c r="B222" t="n">
+        <v>0.023107</v>
+      </c>
+      <c r="C222" t="n">
+        <v>0.024243</v>
+      </c>
+      <c r="D222" t="n">
+        <v>0.025613</v>
+      </c>
+      <c r="E222" t="n">
+        <v>0.057326</v>
+      </c>
+      <c r="F222" t="n">
+        <v>0.06934899999999999</v>
+      </c>
+    </row>
+    <row r="223">
+      <c r="A223" t="inlineStr">
+        <is>
+          <t>2. 对称轴157张/花语.JPG</t>
+        </is>
+      </c>
+      <c r="B223" t="n">
+        <v>0.029785</v>
+      </c>
+      <c r="C223" t="n">
+        <v>0.025692</v>
+      </c>
+      <c r="D223" t="n">
+        <v>0.014349</v>
+      </c>
+      <c r="E223" t="n">
+        <v>0.048316</v>
+      </c>
+      <c r="F223" t="n">
+        <v>0.033222</v>
+      </c>
+    </row>
+    <row r="224">
+      <c r="A224" t="inlineStr">
+        <is>
+          <t>2. 对称轴157张/蒋明明.JPG</t>
+        </is>
+      </c>
+      <c r="B224" t="n">
+        <v>0.032167</v>
+      </c>
+      <c r="C224" t="n">
+        <v>0.028058</v>
+      </c>
+      <c r="D224" t="n">
+        <v>0.074155</v>
+      </c>
+      <c r="E224" t="n">
+        <v>0.050824</v>
+      </c>
+      <c r="F224" t="n">
+        <v>0.108121</v>
+      </c>
+    </row>
+    <row r="225">
+      <c r="A225" t="inlineStr">
+        <is>
+          <t>2. 对称轴157张/蒋洪.JPG</t>
+        </is>
+      </c>
+      <c r="B225" t="n">
+        <v>0.029567</v>
+      </c>
+      <c r="C225" t="n">
+        <v>0.020076</v>
+      </c>
+      <c r="D225" t="n">
+        <v>0.012059</v>
+      </c>
+      <c r="E225" t="n">
+        <v>0.03883</v>
+      </c>
+      <c r="F225" t="n">
+        <v>0.097194</v>
+      </c>
+    </row>
+    <row r="226">
+      <c r="A226" t="inlineStr">
+        <is>
+          <t>2. 对称轴157张/蒋雅竹.JPG</t>
+        </is>
+      </c>
+      <c r="B226" t="n">
+        <v>0.025763</v>
+      </c>
+      <c r="C226" t="n">
+        <v>0.01682</v>
+      </c>
+      <c r="D226" t="n">
+        <v>0.017626</v>
+      </c>
+      <c r="E226" t="n">
+        <v>0.017891</v>
+      </c>
+      <c r="F226" t="n">
+        <v>0.046829</v>
+      </c>
+    </row>
+    <row r="227">
+      <c r="A227" t="inlineStr">
+        <is>
+          <t>2. 对称轴157张/解陈群.JPG</t>
+        </is>
+      </c>
+      <c r="B227" t="n">
+        <v>0.02818</v>
+      </c>
+      <c r="C227" t="n">
+        <v>0.016484</v>
+      </c>
+      <c r="D227" t="n">
+        <v>0.013174</v>
+      </c>
+      <c r="E227" t="n">
+        <v>0.033992</v>
+      </c>
+      <c r="F227" t="n">
+        <v>0.052088</v>
+      </c>
+    </row>
+    <row r="228">
+      <c r="A228" t="inlineStr">
+        <is>
+          <t>2. 对称轴157张/谷俊杰.JPG</t>
+        </is>
+      </c>
+      <c r="B228" t="n">
+        <v>0.048159</v>
+      </c>
+      <c r="C228" t="n">
+        <v>0.029756</v>
+      </c>
+      <c r="D228" t="n">
+        <v>0.064026</v>
+      </c>
+      <c r="E228" t="n">
+        <v>0.089598</v>
+      </c>
+      <c r="F228" t="n">
+        <v>0.132246</v>
+      </c>
+    </row>
+    <row r="229">
+      <c r="A229" t="inlineStr">
+        <is>
+          <t>2. 对称轴157张/贺冬梅.JPG</t>
+        </is>
+      </c>
+      <c r="B229" t="n">
+        <v>0.038596</v>
+      </c>
+      <c r="C229" t="n">
+        <v>0.017992</v>
+      </c>
+      <c r="D229" t="n">
+        <v>0.010968</v>
+      </c>
+      <c r="E229" t="n">
+        <v>0.024443</v>
+      </c>
+      <c r="F229" t="n">
+        <v>0.029146</v>
+      </c>
+    </row>
+    <row r="230">
+      <c r="A230" t="inlineStr">
+        <is>
+          <t>2. 对称轴157张/贺宇翔.JPG</t>
+        </is>
+      </c>
+      <c r="B230" t="n">
+        <v>0.036736</v>
+      </c>
+      <c r="C230" t="n">
+        <v>0.028833</v>
+      </c>
+      <c r="D230" t="n">
+        <v>0.019571</v>
+      </c>
+      <c r="E230" t="n">
+        <v>0.028799</v>
+      </c>
+      <c r="F230" t="n">
+        <v>0.081035</v>
+      </c>
+    </row>
+    <row r="231">
+      <c r="A231" t="inlineStr">
+        <is>
+          <t>2. 对称轴157张/贺灿.JPG</t>
+        </is>
+      </c>
+      <c r="B231" t="n">
+        <v>0.017917</v>
+      </c>
+      <c r="C231" t="n">
+        <v>0.015614</v>
+      </c>
+      <c r="D231" t="n">
+        <v>0.018375</v>
+      </c>
+      <c r="E231" t="n">
+        <v>0.018937</v>
+      </c>
+      <c r="F231" t="n">
+        <v>0.004636</v>
+      </c>
+    </row>
+    <row r="232">
+      <c r="A232" t="inlineStr">
+        <is>
+          <t>2. 对称轴157张/贺露.JPG</t>
+        </is>
+      </c>
+      <c r="B232" t="n">
+        <v>0.030689</v>
+      </c>
+      <c r="C232" t="n">
+        <v>0.016061</v>
+      </c>
+      <c r="D232" t="n">
+        <v>0.015431</v>
+      </c>
+      <c r="E232" t="n">
+        <v>0.022728</v>
+      </c>
+      <c r="F232" t="n">
+        <v>0.006071</v>
+      </c>
+    </row>
+    <row r="233">
+      <c r="A233" t="inlineStr">
+        <is>
+          <t>2. 对称轴157张/贾愔棋.JPG</t>
+        </is>
+      </c>
+      <c r="B233" t="n">
+        <v>0.012323</v>
+      </c>
+      <c r="C233" t="n">
+        <v>0.023645</v>
+      </c>
+      <c r="D233" t="n">
+        <v>0.018846</v>
+      </c>
+      <c r="E233" t="n">
+        <v>0.026304</v>
+      </c>
+      <c r="F233" t="n">
+        <v>0.068678</v>
+      </c>
+    </row>
+    <row r="234">
+      <c r="A234" t="inlineStr">
+        <is>
+          <t>2. 对称轴157张/贾浩宇.JPG</t>
+        </is>
+      </c>
+      <c r="B234" t="n">
+        <v>0.021124</v>
+      </c>
+      <c r="C234" t="n">
+        <v>0.01141</v>
+      </c>
+      <c r="D234" t="n">
+        <v>0.016985</v>
+      </c>
+      <c r="E234" t="n">
+        <v>0.029034</v>
+      </c>
+      <c r="F234" t="n">
+        <v>0.047349</v>
+      </c>
+    </row>
+    <row r="235">
+      <c r="A235" t="inlineStr">
+        <is>
+          <t>2. 对称轴157张/贾茹.JPG</t>
+        </is>
+      </c>
+      <c r="B235" t="n">
+        <v>0.019115</v>
+      </c>
+      <c r="C235" t="n">
+        <v>0.012844</v>
+      </c>
+      <c r="D235" t="n">
+        <v>0.008866000000000001</v>
+      </c>
+      <c r="E235" t="n">
+        <v>0.030955</v>
+      </c>
+      <c r="F235" t="n">
+        <v>0.04147</v>
+      </c>
+    </row>
+    <row r="236">
+      <c r="A236" t="inlineStr">
+        <is>
+          <t>2. 对称轴157张/赖俊颖.JPG</t>
+        </is>
+      </c>
+      <c r="B236" t="n">
+        <v>0.033764</v>
+      </c>
+      <c r="C236" t="n">
+        <v>0.013808</v>
+      </c>
+      <c r="D236" t="n">
+        <v>0.004714</v>
+      </c>
+      <c r="E236" t="n">
+        <v>0.016189</v>
+      </c>
+      <c r="F236" t="n">
+        <v>0.014677</v>
+      </c>
+    </row>
+    <row r="237">
+      <c r="A237" t="inlineStr">
+        <is>
+          <t>2. 对称轴157张/赖婷.JPG</t>
+        </is>
+      </c>
+      <c r="B237" t="n">
+        <v>0.077875</v>
+      </c>
+      <c r="C237" t="n">
+        <v>0.034632</v>
+      </c>
+      <c r="D237" t="n">
+        <v>0.012336</v>
+      </c>
+      <c r="E237" t="n">
+        <v>0.055993</v>
+      </c>
+      <c r="F237" t="n">
+        <v>0.056654</v>
+      </c>
+    </row>
+    <row r="238">
+      <c r="A238" t="inlineStr">
+        <is>
+          <t>2. 对称轴157张/赖巧.JPG</t>
+        </is>
+      </c>
+      <c r="B238" t="n">
+        <v>0.018872</v>
+      </c>
+      <c r="C238" t="n">
+        <v>0.024224</v>
+      </c>
+      <c r="D238" t="n">
+        <v>0.011546</v>
+      </c>
+      <c r="E238" t="n">
+        <v>0.031471</v>
+      </c>
+      <c r="F238" t="n">
+        <v>0.018158</v>
+      </c>
+    </row>
+    <row r="239">
+      <c r="A239" t="inlineStr">
+        <is>
+          <t>2. 对称轴157张/郭优美.JPG</t>
+        </is>
+      </c>
+      <c r="B239" t="n">
+        <v>0.033256</v>
+      </c>
+      <c r="C239" t="n">
+        <v>0.01448</v>
+      </c>
+      <c r="D239" t="n">
+        <v>0.011756</v>
+      </c>
+      <c r="E239" t="n">
+        <v>0.017386</v>
+      </c>
+      <c r="F239" t="n">
+        <v>0.009077</v>
+      </c>
+    </row>
+    <row r="240">
+      <c r="A240" t="inlineStr">
+        <is>
+          <t>2. 对称轴157张/郭子雅.JPG</t>
+        </is>
+      </c>
+      <c r="B240" t="n">
+        <v>0.029501</v>
+      </c>
+      <c r="C240" t="n">
+        <v>0.016991</v>
+      </c>
+      <c r="D240" t="n">
+        <v>0.00702</v>
+      </c>
+      <c r="E240" t="n">
+        <v>0.008649</v>
+      </c>
+      <c r="F240" t="n">
+        <v>0.09095499999999999</v>
+      </c>
+    </row>
+    <row r="241">
+      <c r="A241" t="inlineStr">
+        <is>
+          <t>2. 对称轴157张/郭晶.JPG</t>
+        </is>
+      </c>
+      <c r="B241" t="n">
+        <v>0.025285</v>
+      </c>
+      <c r="C241" t="n">
+        <v>0.020675</v>
+      </c>
+      <c r="D241" t="n">
+        <v>0.004303</v>
+      </c>
+      <c r="E241" t="n">
+        <v>0.014728</v>
+      </c>
+      <c r="F241" t="n">
+        <v>0.012577</v>
+      </c>
+    </row>
+    <row r="242">
+      <c r="A242" t="inlineStr">
+        <is>
+          <t>2. 对称轴157张/郭燕.JPG</t>
+        </is>
+      </c>
+      <c r="B242" t="n">
+        <v>0.019362</v>
+      </c>
+      <c r="C242" t="n">
+        <v>0.009757</v>
+      </c>
+      <c r="D242" t="n">
+        <v>0.017569</v>
+      </c>
+      <c r="E242" t="n">
+        <v>0.019534</v>
+      </c>
+      <c r="F242" t="n">
+        <v>0.043133</v>
+      </c>
+    </row>
+    <row r="243">
+      <c r="A243" t="inlineStr">
+        <is>
+          <t>2. 对称轴157张/郭达.JPG</t>
+        </is>
+      </c>
+      <c r="B243" t="n">
+        <v>0.018736</v>
+      </c>
+      <c r="C243" t="n">
+        <v>0.013149</v>
+      </c>
+      <c r="D243" t="n">
+        <v>0.023136</v>
+      </c>
+      <c r="E243" t="n">
+        <v>0.009235999999999999</v>
+      </c>
+      <c r="F243" t="n">
+        <v>0.062583</v>
+      </c>
+    </row>
+    <row r="244">
+      <c r="A244" t="inlineStr">
+        <is>
+          <t>2. 对称轴157张/郭露.JPG</t>
+        </is>
+      </c>
+      <c r="B244" t="n">
+        <v>0.018855</v>
+      </c>
+      <c r="C244" t="n">
+        <v>0.0222</v>
+      </c>
+      <c r="D244" t="n">
+        <v>0.011013</v>
+      </c>
+      <c r="E244" t="n">
+        <v>0.018323</v>
+      </c>
+      <c r="F244" t="n">
+        <v>0.025376</v>
+      </c>
+    </row>
+    <row r="245">
+      <c r="A245" t="inlineStr">
+        <is>
+          <t>2. 对称轴157张/金浩苒.JPG</t>
+        </is>
+      </c>
+      <c r="B245" t="n">
+        <v>0.041404</v>
+      </c>
+      <c r="C245" t="n">
+        <v>0.020922</v>
+      </c>
+      <c r="D245" t="n">
+        <v>0.018445</v>
+      </c>
+      <c r="E245" t="n">
+        <v>0.045413</v>
+      </c>
+      <c r="F245" t="n">
+        <v>0.044117</v>
+      </c>
+    </row>
+    <row r="246">
+      <c r="A246" t="inlineStr">
+        <is>
+          <t>2. 对称轴157张/雷丽.JPG</t>
+        </is>
+      </c>
+      <c r="B246" t="n">
+        <v>0.022583</v>
+      </c>
+      <c r="C246" t="n">
+        <v>0.014369</v>
+      </c>
+      <c r="D246" t="n">
+        <v>0.03716</v>
+      </c>
+      <c r="E246" t="n">
+        <v>0.039391</v>
+      </c>
+      <c r="F246" t="n">
+        <v>0.085701</v>
+      </c>
+    </row>
+    <row r="247">
+      <c r="A247" t="inlineStr">
+        <is>
+          <t>2. 对称轴157张/雷诗琪.JPG</t>
+        </is>
+      </c>
+      <c r="B247" t="n">
+        <v>0.021963</v>
+      </c>
+      <c r="C247" t="n">
+        <v>0.02535</v>
+      </c>
+      <c r="D247" t="n">
+        <v>0.008160000000000001</v>
+      </c>
+      <c r="E247" t="n">
+        <v>0.019765</v>
+      </c>
+      <c r="F247" t="n">
+        <v>0.042078</v>
+      </c>
+    </row>
+    <row r="248">
+      <c r="A248" t="inlineStr">
+        <is>
+          <t>2. 对称轴157张/雷雯.JPG</t>
+        </is>
+      </c>
+      <c r="B248" t="n">
+        <v>0.019516</v>
+      </c>
+      <c r="C248" t="n">
+        <v>0.020603</v>
+      </c>
+      <c r="D248" t="n">
+        <v>0.002592</v>
+      </c>
+      <c r="E248" t="n">
+        <v>0.016597</v>
+      </c>
+      <c r="F248" t="n">
+        <v>0.042408</v>
+      </c>
+    </row>
+    <row r="249">
+      <c r="A249" t="inlineStr">
+        <is>
+          <t>2. 对称轴157张/韩俊.JPG</t>
+        </is>
+      </c>
+      <c r="B249" t="n">
+        <v>0.018407</v>
+      </c>
+      <c r="C249" t="n">
+        <v>0.019485</v>
+      </c>
+      <c r="D249" t="n">
+        <v>0.015397</v>
+      </c>
+      <c r="E249" t="n">
+        <v>0.009575999999999999</v>
+      </c>
+      <c r="F249" t="n">
+        <v>0.033595</v>
+      </c>
+    </row>
+    <row r="250">
+      <c r="A250" t="inlineStr">
+        <is>
+          <t>2. 对称轴157张/韩知彤.JPG</t>
+        </is>
+      </c>
+      <c r="B250" t="n">
+        <v>0.040273</v>
+      </c>
+      <c r="C250" t="n">
+        <v>0.021294</v>
+      </c>
+      <c r="D250" t="n">
+        <v>0.015794</v>
+      </c>
+      <c r="E250" t="n">
+        <v>0.01485</v>
+      </c>
+      <c r="F250" t="n">
+        <v>0.029864</v>
+      </c>
+    </row>
+    <row r="251">
+      <c r="A251" t="inlineStr">
+        <is>
+          <t>2. 对称轴157张/顾振西.JPG</t>
+        </is>
+      </c>
+      <c r="B251" t="n">
+        <v>0.02166</v>
+      </c>
+      <c r="C251" t="n">
+        <v>0.01928</v>
+      </c>
+      <c r="D251" t="n">
+        <v>0.01065</v>
+      </c>
+      <c r="E251" t="n">
+        <v>0.028918</v>
+      </c>
+      <c r="F251" t="n">
+        <v>0.08810999999999999</v>
+      </c>
+    </row>
+    <row r="252">
+      <c r="A252" t="inlineStr">
+        <is>
+          <t>2. 对称轴157张/高妍妍.JPG</t>
+        </is>
+      </c>
+      <c r="B252" t="n">
+        <v>0.057569</v>
+      </c>
+      <c r="C252" t="n">
+        <v>0.028985</v>
+      </c>
+      <c r="D252" t="n">
+        <v>0.019878</v>
+      </c>
+      <c r="E252" t="n">
+        <v>0.03612</v>
+      </c>
+      <c r="F252" t="n">
+        <v>0.022567</v>
+      </c>
+    </row>
+    <row r="253">
+      <c r="A253" t="inlineStr">
+        <is>
+          <t>2. 对称轴157张/高小果.JPG</t>
+        </is>
+      </c>
+      <c r="B253" t="n">
+        <v>0.015281</v>
+      </c>
+      <c r="C253" t="n">
+        <v>0.016945</v>
+      </c>
+      <c r="D253" t="n">
+        <v>0.019273</v>
+      </c>
+      <c r="E253" t="n">
+        <v>0.026494</v>
+      </c>
+      <c r="F253" t="n">
+        <v>0.038534</v>
+      </c>
+    </row>
+    <row r="254">
+      <c r="A254" t="inlineStr">
+        <is>
+          <t>2. 对称轴157张/高文婷.JPG</t>
+        </is>
+      </c>
+      <c r="B254" t="n">
+        <v>0.014634</v>
+      </c>
+      <c r="C254" t="n">
+        <v>0.017269</v>
+      </c>
+      <c r="D254" t="n">
+        <v>0.017008</v>
+      </c>
+      <c r="E254" t="n">
+        <v>0.011478</v>
+      </c>
+      <c r="F254" t="n">
+        <v>0.035374</v>
+      </c>
+    </row>
+    <row r="255">
+      <c r="A255" t="inlineStr">
+        <is>
+          <t>2. 对称轴157张/高文桢.JPG</t>
+        </is>
+      </c>
+      <c r="B255" t="n">
+        <v>0.035909</v>
+      </c>
+      <c r="C255" t="n">
+        <v>0.029916</v>
+      </c>
+      <c r="D255" t="n">
+        <v>0.018543</v>
+      </c>
+      <c r="E255" t="n">
+        <v>0.022379</v>
+      </c>
+      <c r="F255" t="n">
+        <v>0.004125</v>
+      </c>
+    </row>
+    <row r="256">
+      <c r="A256" t="inlineStr">
+        <is>
+          <t>2. 对称轴157张/高春梅.JPG</t>
+        </is>
+      </c>
+      <c r="B256" t="n">
+        <v>0.035313</v>
+      </c>
+      <c r="C256" t="n">
+        <v>0.020007</v>
+      </c>
+      <c r="D256" t="n">
+        <v>0.035921</v>
+      </c>
+      <c r="E256" t="n">
+        <v>0.043666</v>
+      </c>
+      <c r="F256" t="n">
+        <v>0.048657</v>
+      </c>
+    </row>
+    <row r="257">
+      <c r="A257" t="inlineStr">
+        <is>
+          <t>2. 对称轴157张/高林静.JPG</t>
+        </is>
+      </c>
+      <c r="B257" t="n">
+        <v>0.023671</v>
+      </c>
+      <c r="C257" t="n">
+        <v>0.021246</v>
+      </c>
+      <c r="D257" t="n">
+        <v>0.020847</v>
+      </c>
+      <c r="E257" t="n">
+        <v>0.02384</v>
+      </c>
+      <c r="F257" t="n">
+        <v>0.101422</v>
+      </c>
+    </row>
+    <row r="258">
+      <c r="A258" t="inlineStr">
+        <is>
+          <t>2. 对称轴157张/高雨洁.JPG</t>
+        </is>
+      </c>
+      <c r="B258" t="n">
+        <v>0.032482</v>
+      </c>
+      <c r="C258" t="n">
+        <v>0.016301</v>
+      </c>
+      <c r="D258" t="n">
+        <v>0.027542</v>
+      </c>
+      <c r="E258" t="n">
+        <v>0.042738</v>
+      </c>
+      <c r="F258" t="n">
+        <v>0.041885</v>
+      </c>
+    </row>
+    <row r="259">
+      <c r="A259" t="inlineStr">
+        <is>
+          <t>2. 对称轴157张/高静文.JPG</t>
+        </is>
+      </c>
+      <c r="B259" t="n">
+        <v>0.027581</v>
+      </c>
+      <c r="C259" t="n">
+        <v>0.011975</v>
+      </c>
+      <c r="D259" t="n">
+        <v>0.006579</v>
+      </c>
+      <c r="E259" t="n">
+        <v>0.026015</v>
+      </c>
+      <c r="F259" t="n">
+        <v>0.010385</v>
+      </c>
+    </row>
+    <row r="260">
+      <c r="A260" t="inlineStr">
+        <is>
+          <t>2. 对称轴157张/黄博.JPG</t>
+        </is>
+      </c>
+      <c r="B260" t="n">
+        <v>0.019015</v>
+      </c>
+      <c r="C260" t="n">
+        <v>0.01483</v>
+      </c>
+      <c r="D260" t="n">
+        <v>0.002965</v>
+      </c>
+      <c r="E260" t="n">
+        <v>0.04041</v>
+      </c>
+      <c r="F260" t="n">
+        <v>0.043615</v>
+      </c>
+    </row>
+    <row r="261">
+      <c r="A261" t="inlineStr">
+        <is>
+          <t>2. 对称轴157张/黄卫.JPG</t>
+        </is>
+      </c>
+      <c r="B261" t="n">
+        <v>0.030503</v>
+      </c>
+      <c r="C261" t="n">
+        <v>0.0141</v>
+      </c>
+      <c r="D261" t="n">
+        <v>0.045748</v>
+      </c>
+      <c r="E261" t="n">
+        <v>0.057366</v>
+      </c>
+      <c r="F261" t="n">
+        <v>0.09243700000000001</v>
+      </c>
+    </row>
+    <row r="262">
+      <c r="A262" t="inlineStr">
+        <is>
+          <t>2. 对称轴157张/黄媛.JPG</t>
+        </is>
+      </c>
+      <c r="B262" t="n">
+        <v>0.028067</v>
+      </c>
+      <c r="C262" t="n">
+        <v>0.01843</v>
+      </c>
+      <c r="D262" t="n">
+        <v>0.02199</v>
+      </c>
+      <c r="E262" t="n">
+        <v>0.032805</v>
+      </c>
+      <c r="F262" t="n">
+        <v>0.028028</v>
+      </c>
+    </row>
+    <row r="263">
+      <c r="A263" t="inlineStr">
+        <is>
+          <t>2. 对称轴157张/黄子淇.JPG</t>
+        </is>
+      </c>
+      <c r="B263" t="n">
+        <v>0.0314</v>
+      </c>
+      <c r="C263" t="n">
+        <v>0.032566</v>
+      </c>
+      <c r="D263" t="n">
+        <v>0.01286</v>
+      </c>
+      <c r="E263" t="n">
+        <v>0.03769</v>
+      </c>
+      <c r="F263" t="n">
+        <v>0.05265</v>
+      </c>
+    </row>
+    <row r="264">
+      <c r="A264" t="inlineStr">
+        <is>
+          <t>2. 对称轴157张/黄志婉.JPG</t>
+        </is>
+      </c>
+      <c r="B264" t="n">
+        <v>0.02968</v>
+      </c>
+      <c r="C264" t="n">
+        <v>0.016637</v>
+      </c>
+      <c r="D264" t="n">
+        <v>0.032697</v>
+      </c>
+      <c r="E264" t="n">
+        <v>0.013804</v>
+      </c>
+      <c r="F264" t="n">
+        <v>0.05059</v>
+      </c>
+    </row>
+    <row r="265">
+      <c r="A265" t="inlineStr">
+        <is>
+          <t>2. 对称轴157张/黄思敏.JPG</t>
+        </is>
+      </c>
+      <c r="B265" t="n">
+        <v>0.016024</v>
+      </c>
+      <c r="C265" t="n">
+        <v>0.023212</v>
+      </c>
+      <c r="D265" t="n">
+        <v>0.016982</v>
+      </c>
+      <c r="E265" t="n">
+        <v>0.020709</v>
+      </c>
+      <c r="F265" t="n">
+        <v>0.044214</v>
+      </c>
+    </row>
+    <row r="266">
+      <c r="A266" t="inlineStr">
+        <is>
+          <t>2. 对称轴157张/黄朝民.JPG</t>
+        </is>
+      </c>
+      <c r="B266" t="n">
+        <v>0.013537</v>
+      </c>
+      <c r="C266" t="n">
+        <v>0.007182</v>
+      </c>
+      <c r="D266" t="n">
+        <v>0.011924</v>
+      </c>
+      <c r="E266" t="n">
+        <v>0.013642</v>
+      </c>
+      <c r="F266" t="n">
+        <v>0.028392</v>
+      </c>
+    </row>
+    <row r="267">
+      <c r="A267" t="inlineStr">
+        <is>
+          <t>2. 对称轴157张/黄柳依.JPG</t>
+        </is>
+      </c>
+      <c r="B267" t="n">
+        <v>0.036948</v>
+      </c>
+      <c r="C267" t="n">
+        <v>0.015266</v>
+      </c>
+      <c r="D267" t="n">
+        <v>0.028362</v>
+      </c>
+      <c r="E267" t="n">
+        <v>0.021548</v>
+      </c>
+      <c r="F267" t="n">
+        <v>0.06385399999999999</v>
+      </c>
+    </row>
+    <row r="268">
+      <c r="A268" t="inlineStr">
+        <is>
+          <t>2. 对称轴157张/黄楷译.JPG</t>
+        </is>
+      </c>
+      <c r="B268" t="n">
+        <v>0.021325</v>
+      </c>
+      <c r="C268" t="n">
+        <v>0.013396</v>
+      </c>
+      <c r="D268" t="n">
+        <v>0.033366</v>
+      </c>
+      <c r="E268" t="n">
+        <v>0.056482</v>
+      </c>
+      <c r="F268" t="n">
+        <v>0.137818</v>
+      </c>
+    </row>
+    <row r="269">
+      <c r="A269" t="inlineStr">
+        <is>
+          <t>2. 对称轴157张/黄欣悦.JPG</t>
+        </is>
+      </c>
+      <c r="B269" t="n">
+        <v>0.035845</v>
+      </c>
+      <c r="C269" t="n">
+        <v>0.015312</v>
+      </c>
+      <c r="D269" t="n">
+        <v>0.009368</v>
+      </c>
+      <c r="E269" t="n">
+        <v>0.030379</v>
+      </c>
+      <c r="F269" t="n">
+        <v>0.028525</v>
+      </c>
+    </row>
+    <row r="270">
+      <c r="A270" t="inlineStr">
+        <is>
+          <t>2. 对称轴157张/黄洪秀.JPG</t>
+        </is>
+      </c>
+      <c r="B270" t="n">
+        <v>0.030536</v>
+      </c>
+      <c r="C270" t="n">
+        <v>0.007727</v>
+      </c>
+      <c r="D270" t="n">
+        <v>0.006957</v>
+      </c>
+      <c r="E270" t="n">
+        <v>0.016</v>
+      </c>
+      <c r="F270" t="n">
+        <v>0.098681</v>
+      </c>
+    </row>
+    <row r="271">
+      <c r="A271" t="inlineStr">
+        <is>
+          <t>2. 对称轴157张/黄瑾乔.JPG</t>
+        </is>
+      </c>
+      <c r="B271" t="n">
+        <v>0.045299</v>
+      </c>
+      <c r="C271" t="n">
+        <v>0.030869</v>
+      </c>
+      <c r="D271" t="n">
+        <v>0.038164</v>
+      </c>
+      <c r="E271" t="n">
+        <v>0.07092900000000001</v>
+      </c>
+      <c r="F271" t="n">
+        <v>0.103266</v>
+      </c>
+    </row>
+    <row r="272">
+      <c r="A272" t="inlineStr">
+        <is>
+          <t>2. 对称轴157张/黄真.JPG</t>
+        </is>
+      </c>
+      <c r="B272" t="n">
+        <v>0.021621</v>
+      </c>
+      <c r="C272" t="n">
+        <v>0.012564</v>
+      </c>
+      <c r="D272" t="n">
+        <v>0.009271</v>
+      </c>
+      <c r="E272" t="n">
+        <v>0.041347</v>
+      </c>
+      <c r="F272" t="n">
+        <v>0.068273</v>
+      </c>
+    </row>
+    <row r="273">
+      <c r="A273" t="inlineStr">
+        <is>
+          <t>2. 对称轴157张/黄箐.JPG</t>
+        </is>
+      </c>
+      <c r="B273" t="n">
+        <v>0.018313</v>
+      </c>
+      <c r="C273" t="n">
+        <v>0.02077</v>
+      </c>
+      <c r="D273" t="n">
+        <v>0.0315</v>
+      </c>
+      <c r="E273" t="n">
+        <v>0.026075</v>
+      </c>
+      <c r="F273" t="n">
+        <v>0.034062</v>
+      </c>
+    </row>
+    <row r="274">
+      <c r="A274" t="inlineStr">
+        <is>
+          <t>2. 对称轴157张/黄纯.JPG</t>
+        </is>
+      </c>
+      <c r="B274" t="n">
+        <v>0.0354</v>
+      </c>
+      <c r="C274" t="n">
+        <v>0.010234</v>
+      </c>
+      <c r="D274" t="n">
+        <v>0.020329</v>
+      </c>
+      <c r="E274" t="n">
+        <v>0.011987</v>
+      </c>
+      <c r="F274" t="n">
+        <v>0.045765</v>
+      </c>
+    </row>
+    <row r="275">
+      <c r="A275" t="inlineStr">
+        <is>
+          <t>2. 对称轴157张/黄耕宁.JPG</t>
+        </is>
+      </c>
+      <c r="B275" t="n">
+        <v>0.014452</v>
+      </c>
+      <c r="C275" t="n">
+        <v>0.006757</v>
+      </c>
+      <c r="D275" t="n">
+        <v>0.014331</v>
+      </c>
+      <c r="E275" t="n">
+        <v>0.018664</v>
+      </c>
+      <c r="F275" t="n">
+        <v>0.04263</v>
+      </c>
+    </row>
+    <row r="276">
+      <c r="A276" t="inlineStr">
+        <is>
+          <t>2. 对称轴157张/黄良晴.JPG</t>
+        </is>
+      </c>
+      <c r="B276" t="n">
+        <v>0.054366</v>
+      </c>
+      <c r="C276" t="n">
+        <v>0.023206</v>
+      </c>
+      <c r="D276" t="n">
+        <v>0.026004</v>
+      </c>
+      <c r="E276" t="n">
+        <v>0.052615</v>
+      </c>
+      <c r="F276" t="n">
+        <v>0.046776</v>
+      </c>
+    </row>
+    <row r="277">
+      <c r="A277" t="inlineStr">
+        <is>
+          <t>2. 对称轴157张/黄芝霖.JPG</t>
+        </is>
+      </c>
+      <c r="B277" t="n">
+        <v>0.025487</v>
+      </c>
+      <c r="C277" t="n">
+        <v>0.008538</v>
+      </c>
+      <c r="D277" t="n">
+        <v>0.030383</v>
+      </c>
+      <c r="E277" t="n">
+        <v>0.016858</v>
+      </c>
+      <c r="F277" t="n">
+        <v>0.048794</v>
+      </c>
+    </row>
+    <row r="278">
+      <c r="A278" t="inlineStr">
+        <is>
+          <t>2. 对称轴157张/黄莞淳.JPG</t>
+        </is>
+      </c>
+      <c r="B278" t="n">
+        <v>0.044789</v>
+      </c>
+      <c r="C278" t="n">
+        <v>0.027368</v>
+      </c>
+      <c r="D278" t="n">
+        <v>0.001213</v>
+      </c>
+      <c r="E278" t="n">
+        <v>0.020422</v>
+      </c>
+      <c r="F278" t="n">
+        <v>0.087743</v>
+      </c>
+    </row>
+    <row r="279">
+      <c r="A279" t="inlineStr">
+        <is>
+          <t>2. 对称轴157张/黄诗航.JPG</t>
+        </is>
+      </c>
+      <c r="B279" t="n">
+        <v>0.036829</v>
+      </c>
+      <c r="C279" t="n">
+        <v>0.013142</v>
+      </c>
+      <c r="D279" t="n">
+        <v>0.011674</v>
+      </c>
+      <c r="E279" t="n">
+        <v>0.016563</v>
+      </c>
+      <c r="F279" t="n">
+        <v>0.040114</v>
+      </c>
+    </row>
+    <row r="280">
+      <c r="A280" t="inlineStr">
+        <is>
+          <t>2. 对称轴157张/黄雪梅.JPG</t>
+        </is>
+      </c>
+      <c r="B280" t="n">
+        <v>0.015637</v>
+      </c>
+      <c r="C280" t="n">
+        <v>0.009820000000000001</v>
+      </c>
+      <c r="D280" t="n">
+        <v>0.020376</v>
+      </c>
+      <c r="E280" t="n">
+        <v>0.020745</v>
+      </c>
+      <c r="F280" t="n">
+        <v>0.050691</v>
+      </c>
+    </row>
+    <row r="281">
+      <c r="A281" t="inlineStr">
+        <is>
+          <t>2. 对称轴157张/黄雪瑶.JPG</t>
+        </is>
+      </c>
+      <c r="B281" t="n">
+        <v>0.021515</v>
+      </c>
+      <c r="C281" t="n">
+        <v>0.027934</v>
+      </c>
+      <c r="D281" t="n">
+        <v>0.020936</v>
+      </c>
+      <c r="E281" t="n">
+        <v>0.02107</v>
+      </c>
+      <c r="F281" t="n">
+        <v>0.016317</v>
+      </c>
+    </row>
+    <row r="282">
+      <c r="A282" t="inlineStr">
+        <is>
+          <t>2. 对称轴157张/黎火金.JPG</t>
+        </is>
+      </c>
+      <c r="B282" t="n">
+        <v>0.026382</v>
+      </c>
+      <c r="C282" t="n">
+        <v>0.016355</v>
+      </c>
+      <c r="D282" t="n">
+        <v>0.01997</v>
+      </c>
+      <c r="E282" t="n">
+        <v>0.033732</v>
+      </c>
+      <c r="F282" t="n">
+        <v>0.051789</v>
+      </c>
+    </row>
+    <row r="283">
+      <c r="A283" t="inlineStr">
+        <is>
+          <t>2. 对称轴157张/龚圣华.JPG</t>
+        </is>
+      </c>
+      <c r="B283" t="n">
+        <v>0.02822</v>
+      </c>
+      <c r="C283" t="n">
+        <v>0.020468</v>
+      </c>
+      <c r="D283" t="n">
+        <v>0.021178</v>
+      </c>
+      <c r="E283" t="n">
+        <v>0.027356</v>
+      </c>
+      <c r="F283" t="n">
+        <v>0.087552</v>
+      </c>
+    </row>
+    <row r="284">
+      <c r="A284" t="inlineStr">
+        <is>
+          <t>2. 对称轴157张/龚必东.JPG</t>
+        </is>
+      </c>
+      <c r="B284" t="n">
+        <v>0.043644</v>
+      </c>
+      <c r="C284" t="n">
+        <v>0.018407</v>
+      </c>
+      <c r="D284" t="n">
+        <v>0.014796</v>
+      </c>
+      <c r="E284" t="n">
+        <v>0.019428</v>
+      </c>
+      <c r="F284" t="n">
+        <v>0.06304</v>
       </c>
     </row>
   </sheetData>
